--- a/Sets-vervestacks.xlsx
+++ b/Sets-vervestacks.xlsx
@@ -5,18 +5,23 @@
   <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_grids\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17681099-9C76-4C6E-A393-D5B8D2AFAF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D317B803-F8B8-4CD7-BB8E-98CBBF2C7720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
     <sheet name="geo_sets" sheetId="3" r:id="rId2"/>
     <sheet name="VEDA_Sets-Proc" sheetId="1" r:id="rId3"/>
+    <sheet name="SetsEditor- Proc" sheetId="4" r:id="rId4"/>
+    <sheet name="SetsEditor- Comm" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SetsEditor- Proc'!$D$2:$F$75</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="748">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -1490,13 +1495,805 @@
   </si>
   <si>
     <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>~TFM_PSets</t>
+  </si>
+  <si>
+    <t>t_pos_andor_forsets</t>
+  </si>
+  <si>
+    <t>t_neg_andor_forsets</t>
+  </si>
+  <si>
+    <t>t_neg_andor</t>
+  </si>
+  <si>
+    <t>setdesc</t>
+  </si>
+  <si>
+    <t>pset_set</t>
+  </si>
+  <si>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>pset_pd</t>
+  </si>
+  <si>
+    <t>Bio</t>
+  </si>
+  <si>
+    <t>ELCWOD</t>
+  </si>
+  <si>
+    <t>Biogas</t>
+  </si>
+  <si>
+    <t>ELCBIG</t>
+  </si>
+  <si>
+    <t>Coal</t>
+  </si>
+  <si>
+    <t>ELCCOA</t>
+  </si>
+  <si>
+    <t>Geothermal</t>
+  </si>
+  <si>
+    <t>ELCGEO</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>ELCHYD</t>
+  </si>
+  <si>
+    <t>Natural Gas</t>
+  </si>
+  <si>
+    <t>ELCNGA</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>ELCSOL</t>
+  </si>
+  <si>
+    <t>E_StgBatt</t>
+  </si>
+  <si>
+    <t>Batt Stg</t>
+  </si>
+  <si>
+    <t>EBAT*</t>
+  </si>
+  <si>
+    <t>E_StgPump</t>
+  </si>
+  <si>
+    <t>Phydro Stg</t>
+  </si>
+  <si>
+    <t>EHYD*</t>
+  </si>
+  <si>
+    <t>Waste</t>
+  </si>
+  <si>
+    <t>MNCWST</t>
+  </si>
+  <si>
+    <t>Wind</t>
+  </si>
+  <si>
+    <t>ELCWIN</t>
+  </si>
+  <si>
+    <t>Aviation</t>
+  </si>
+  <si>
+    <t>T*Jet*</t>
+  </si>
+  <si>
+    <t>Bus</t>
+  </si>
+  <si>
+    <t>T*Bus</t>
+  </si>
+  <si>
+    <t>Cars</t>
+  </si>
+  <si>
+    <t>T*car</t>
+  </si>
+  <si>
+    <t>eu_ClothesDry</t>
+  </si>
+  <si>
+    <t>Clothes dry</t>
+  </si>
+  <si>
+    <t>*-CD*</t>
+  </si>
+  <si>
+    <t>eu_ClothesWash</t>
+  </si>
+  <si>
+    <t>Clothes wash</t>
+  </si>
+  <si>
+    <t>*-CW*</t>
+  </si>
+  <si>
+    <t>eu_Cooking</t>
+  </si>
+  <si>
+    <t>Cooking</t>
+  </si>
+  <si>
+    <t>*-CK*</t>
+  </si>
+  <si>
+    <t>eu_DishWash</t>
+  </si>
+  <si>
+    <t>Dish Wash</t>
+  </si>
+  <si>
+    <t>*-DW*</t>
+  </si>
+  <si>
+    <t>eu_Irrigation</t>
+  </si>
+  <si>
+    <t>Irrigation</t>
+  </si>
+  <si>
+    <t>*-IRG*</t>
+  </si>
+  <si>
+    <t>eu_Lighting</t>
+  </si>
+  <si>
+    <t>Lighting</t>
+  </si>
+  <si>
+    <t>*-LIG*,*-LT*</t>
+  </si>
+  <si>
+    <t>eu_MotivePower</t>
+  </si>
+  <si>
+    <t>Motive Power</t>
+  </si>
+  <si>
+    <t>*-MotP*,*-MP?*</t>
+  </si>
+  <si>
+    <t>Motorcycle</t>
+  </si>
+  <si>
+    <t>T*Mcy</t>
+  </si>
+  <si>
+    <t>eu_ProcessHeat</t>
+  </si>
+  <si>
+    <t>Process Heat</t>
+  </si>
+  <si>
+    <t>*-PH*</t>
+  </si>
+  <si>
+    <t>eu_Pumping</t>
+  </si>
+  <si>
+    <t>Pumping</t>
+  </si>
+  <si>
+    <t>*-pump*,-*-motp*</t>
+  </si>
+  <si>
+    <t>Rail</t>
+  </si>
+  <si>
+    <t>T*Rail</t>
+  </si>
+  <si>
+    <t>eu_Refrigeration</t>
+  </si>
+  <si>
+    <t>Refrigeration</t>
+  </si>
+  <si>
+    <t>*-RF*</t>
+  </si>
+  <si>
+    <t>Ships</t>
+  </si>
+  <si>
+    <t>T*Ship</t>
+  </si>
+  <si>
+    <t>eu_SpaceCool</t>
+  </si>
+  <si>
+    <t>Space Cool</t>
+  </si>
+  <si>
+    <t>*-SC*</t>
+  </si>
+  <si>
+    <t>eu_SpaceHeat</t>
+  </si>
+  <si>
+    <t>Space Heat</t>
+  </si>
+  <si>
+    <t>*-SH*</t>
+  </si>
+  <si>
+    <t>Trucks</t>
+  </si>
+  <si>
+    <t>T*Trk</t>
+  </si>
+  <si>
+    <t>eu_WaterHeat</t>
+  </si>
+  <si>
+    <t>Water Heat</t>
+  </si>
+  <si>
+    <t>*-WH*</t>
+  </si>
+  <si>
+    <t>s_Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>A*</t>
+  </si>
+  <si>
+    <t>s_BioProc</t>
+  </si>
+  <si>
+    <t>Bio Processing</t>
+  </si>
+  <si>
+    <t>-FTE*</t>
+  </si>
+  <si>
+    <t>*wood*,*waste*</t>
+  </si>
+  <si>
+    <t>s_Commercial</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>C[_]*</t>
+  </si>
+  <si>
+    <t>s_Hydrogen</t>
+  </si>
+  <si>
+    <t>Hydrogen Prod</t>
+  </si>
+  <si>
+    <t>-FTE*,*H2*</t>
+  </si>
+  <si>
+    <t>s_Industry</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>IND*</t>
+  </si>
+  <si>
+    <t>s_Power</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>ELE,-STG</t>
+  </si>
+  <si>
+    <t>s_PriExp</t>
+  </si>
+  <si>
+    <t>Primary Exports</t>
+  </si>
+  <si>
+    <t>EXP*</t>
+  </si>
+  <si>
+    <t>s_PriImp</t>
+  </si>
+  <si>
+    <t>Primary Imports</t>
+  </si>
+  <si>
+    <t>IMP*</t>
+  </si>
+  <si>
+    <t>s_PriProd</t>
+  </si>
+  <si>
+    <t>Primary Production</t>
+  </si>
+  <si>
+    <t>MIN*</t>
+  </si>
+  <si>
+    <t>s_Refinery</t>
+  </si>
+  <si>
+    <t>Refinery</t>
+  </si>
+  <si>
+    <t>-FTE*,Ref*</t>
+  </si>
+  <si>
+    <t>s_Residential</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>R[_]*</t>
+  </si>
+  <si>
+    <t>s_Storage</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>s_Transport</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>T[_]*</t>
+  </si>
+  <si>
+    <t>Attached</t>
+  </si>
+  <si>
+    <t>R_JDW*</t>
+  </si>
+  <si>
+    <t>ss_Chemicals</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>CHM*</t>
+  </si>
+  <si>
+    <t>ss_Construction</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>CNST*</t>
+  </si>
+  <si>
+    <t>ss_Dairy</t>
+  </si>
+  <si>
+    <t>Dairy</t>
+  </si>
+  <si>
+    <t>DARY*</t>
+  </si>
+  <si>
+    <t>Dairy Cattle Farming</t>
+  </si>
+  <si>
+    <t>ADCF*</t>
+  </si>
+  <si>
+    <t>Detached</t>
+  </si>
+  <si>
+    <t>R_DDW*</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>C_EDU-*</t>
+  </si>
+  <si>
+    <t>Fishing</t>
+  </si>
+  <si>
+    <t>AFIS*</t>
+  </si>
+  <si>
+    <t>ss_Food</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>FOOD*</t>
+  </si>
+  <si>
+    <t>Forestry</t>
+  </si>
+  <si>
+    <t>AFOR*</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>C_HLTH*</t>
+  </si>
+  <si>
+    <t>Horticulture</t>
+  </si>
+  <si>
+    <t>AHOR*</t>
+  </si>
+  <si>
+    <t>Indoor cropping</t>
+  </si>
+  <si>
+    <t>AIND*</t>
+  </si>
+  <si>
+    <t>Livestock</t>
+  </si>
+  <si>
+    <t>ALIV*</t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
+    <t>MEAT*</t>
+  </si>
+  <si>
+    <t>Metals</t>
+  </si>
+  <si>
+    <t>METAL*</t>
+  </si>
+  <si>
+    <t>Methanol</t>
+  </si>
+  <si>
+    <t>MTHOL*</t>
+  </si>
+  <si>
+    <t>Minerals</t>
+  </si>
+  <si>
+    <t>MNRL*</t>
+  </si>
+  <si>
+    <t>Mining</t>
+  </si>
+  <si>
+    <t>MNNG*</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>C_OFFC*</t>
+  </si>
+  <si>
+    <t>Other Ind</t>
+  </si>
+  <si>
+    <t>OTH-T</t>
+  </si>
+  <si>
+    <t>Other Agri</t>
+  </si>
+  <si>
+    <t>AOTH*</t>
+  </si>
+  <si>
+    <t>Other Com</t>
+  </si>
+  <si>
+    <t>C_OTH-*</t>
+  </si>
+  <si>
+    <t>ss_Paper</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>PLP*</t>
+  </si>
+  <si>
+    <t>Refining</t>
+  </si>
+  <si>
+    <t>REFI*</t>
+  </si>
+  <si>
+    <t>ss_Steel</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>IIS*</t>
+  </si>
+  <si>
+    <t>Urea</t>
+  </si>
+  <si>
+    <t>UREA*</t>
+  </si>
+  <si>
+    <t>Wood Prod Mfg</t>
+  </si>
+  <si>
+    <t>WOOD*</t>
+  </si>
+  <si>
+    <t>WSR</t>
+  </si>
+  <si>
+    <t>C_WSR-*</t>
+  </si>
+  <si>
+    <t>~TFM_CSets</t>
+  </si>
+  <si>
+    <t>cset_set</t>
+  </si>
+  <si>
+    <t>cset_cn</t>
+  </si>
+  <si>
+    <t>cset_cd</t>
+  </si>
+  <si>
+    <t>c_pos_andor_forsets</t>
+  </si>
+  <si>
+    <t>c_pos_andor</t>
+  </si>
+  <si>
+    <t>c_neg_andor_forsets</t>
+  </si>
+  <si>
+    <t>c_neg_andor</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>COA</t>
+  </si>
+  <si>
+    <t>DSL</t>
+  </si>
+  <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricity </t>
+  </si>
+  <si>
+    <t>FOL</t>
+  </si>
+  <si>
+    <t>Fuel Oil</t>
+  </si>
+  <si>
+    <t>GEO</t>
+  </si>
+  <si>
+    <t>H2R</t>
+  </si>
+  <si>
+    <t>Hydrogen</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>NGA</t>
+  </si>
+  <si>
+    <t>PET</t>
+  </si>
+  <si>
+    <t>Petrol</t>
+  </si>
+  <si>
+    <t>PLT</t>
+  </si>
+  <si>
+    <t>Pellet</t>
+  </si>
+  <si>
+    <t>WOD</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>MNR</t>
+  </si>
+  <si>
+    <t>Manure</t>
+  </si>
+  <si>
+    <t>BIG</t>
+  </si>
+  <si>
+    <t>BIL</t>
+  </si>
+  <si>
+    <t>Bioliquid</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>Lignite</t>
+  </si>
+  <si>
+    <t>seq</t>
+  </si>
+  <si>
+    <t>CO2 to CCS</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>DID</t>
+  </si>
+  <si>
+    <t>Drop-In Diesel</t>
+  </si>
+  <si>
+    <t>DIJ</t>
+  </si>
+  <si>
+    <t>Drop-In Jet</t>
+  </si>
+  <si>
+    <t>LCD</t>
+  </si>
+  <si>
+    <t>Electricity Production</t>
+  </si>
+  <si>
+    <t>CDD</t>
+  </si>
+  <si>
+    <t>-HV</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>-MV</t>
+  </si>
+  <si>
+    <t>OIL</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>TID</t>
+  </si>
+  <si>
+    <t>Tidal</t>
+  </si>
+  <si>
+    <t>URN</t>
+  </si>
+  <si>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>WIN</t>
+  </si>
+  <si>
+    <t>H2C</t>
+  </si>
+  <si>
+    <t>Green Hydrogen Green Hydrogen Fuel</t>
+  </si>
+  <si>
+    <t>H2D</t>
+  </si>
+  <si>
+    <t>JET</t>
+  </si>
+  <si>
+    <t>Jet Fuel</t>
+  </si>
+  <si>
+    <t>LNG</t>
+  </si>
+  <si>
+    <t>ILD</t>
+  </si>
+  <si>
+    <t>Crude Oil (domestic)</t>
+  </si>
+  <si>
+    <t>ILI</t>
+  </si>
+  <si>
+    <t>Crude Oil (imported)</t>
+  </si>
+  <si>
+    <t>OTH</t>
+  </si>
+  <si>
+    <t>Other Oil</t>
+  </si>
+  <si>
+    <t>DEM</t>
+  </si>
+  <si>
+    <t>agriculture</t>
+  </si>
+  <si>
+    <t>A*,meat*,D*</t>
+  </si>
+  <si>
+    <t>commercial</t>
+  </si>
+  <si>
+    <t>C*</t>
+  </si>
+  <si>
+    <t>F*,I*,ref*,M*,-meat*,O*,P*,U*,W*</t>
+  </si>
+  <si>
+    <t>residential</t>
+  </si>
+  <si>
+    <t>R*,-ref*</t>
+  </si>
+  <si>
+    <t>T*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1520,13 +2317,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -1556,20 +2366,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
+    <cellStyle name="Neutral 2" xfId="3" xr:uid="{599912E3-8559-451E-9420-BD3F24E264C7}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5615,4 +6429,2138 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A236EA34-5180-48E7-B945-13E283806401}">
+  <dimension ref="A1:K75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" t="s">
+        <v>488</v>
+      </c>
+      <c r="G2" t="s">
+        <v>489</v>
+      </c>
+      <c r="H2" t="s">
+        <v>490</v>
+      </c>
+      <c r="I2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E3" t="str">
+        <f t="shared" ref="E3:E9" si="0">"E_"&amp;SUBSTITUTE(F3," ","")</f>
+        <v>E_Bio</v>
+      </c>
+      <c r="F3" t="s">
+        <v>492</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E4" t="str">
+        <f t="shared" si="0"/>
+        <v>E_Biogas</v>
+      </c>
+      <c r="F4" t="s">
+        <v>494</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v>E_Coal</v>
+      </c>
+      <c r="F5" t="s">
+        <v>496</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>E_Geothermal</v>
+      </c>
+      <c r="F6" t="s">
+        <v>498</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>E_Hydro</v>
+      </c>
+      <c r="F7" t="s">
+        <v>500</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>E_NaturalGas</v>
+      </c>
+      <c r="F8" t="s">
+        <v>502</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>E_Solar</v>
+      </c>
+      <c r="F9" t="s">
+        <v>504</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E10" t="s">
+        <v>506</v>
+      </c>
+      <c r="F10" t="s">
+        <v>507</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E11" t="s">
+        <v>509</v>
+      </c>
+      <c r="F11" t="s">
+        <v>510</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E12" t="str">
+        <f>"E_"&amp;SUBSTITUTE(F12," ","")</f>
+        <v>E_Waste</v>
+      </c>
+      <c r="F12" t="s">
+        <v>512</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E13" t="str">
+        <f>"E_"&amp;SUBSTITUTE(F13," ","")</f>
+        <v>E_Wind</v>
+      </c>
+      <c r="F13" t="s">
+        <v>514</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E14" t="str">
+        <f>"eu_"&amp;F14</f>
+        <v>eu_Aviation</v>
+      </c>
+      <c r="F14" t="s">
+        <v>516</v>
+      </c>
+      <c r="G14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E15" t="str">
+        <f>"eu_"&amp;F15</f>
+        <v>eu_Bus</v>
+      </c>
+      <c r="F15" t="s">
+        <v>518</v>
+      </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="E16" t="str">
+        <f>"eu_"&amp;F16</f>
+        <v>eu_Cars</v>
+      </c>
+      <c r="F16" t="s">
+        <v>520</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="17" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E17" t="s">
+        <v>522</v>
+      </c>
+      <c r="F17" t="s">
+        <v>523</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="18" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E18" t="s">
+        <v>525</v>
+      </c>
+      <c r="F18" t="s">
+        <v>526</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="19" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E19" t="s">
+        <v>528</v>
+      </c>
+      <c r="F19" t="s">
+        <v>529</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="20" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E20" t="s">
+        <v>531</v>
+      </c>
+      <c r="F20" t="s">
+        <v>532</v>
+      </c>
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="21" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E21" t="s">
+        <v>534</v>
+      </c>
+      <c r="F21" t="s">
+        <v>535</v>
+      </c>
+      <c r="G21" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="22" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E22" t="s">
+        <v>537</v>
+      </c>
+      <c r="F22" t="s">
+        <v>538</v>
+      </c>
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="23" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E23" t="s">
+        <v>540</v>
+      </c>
+      <c r="F23" t="s">
+        <v>541</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="24" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E24" t="str">
+        <f>"eu_"&amp;F24</f>
+        <v>eu_Motorcycle</v>
+      </c>
+      <c r="F24" t="s">
+        <v>543</v>
+      </c>
+      <c r="G24" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="25" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E25" t="s">
+        <v>545</v>
+      </c>
+      <c r="F25" t="s">
+        <v>546</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="J25" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="26" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E26" t="s">
+        <v>548</v>
+      </c>
+      <c r="F26" t="s">
+        <v>549</v>
+      </c>
+      <c r="G26" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="27" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E27" t="str">
+        <f>"eu_"&amp;F27</f>
+        <v>eu_Rail</v>
+      </c>
+      <c r="F27" t="s">
+        <v>551</v>
+      </c>
+      <c r="G27" t="s">
+        <v>49</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="28" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E28" t="s">
+        <v>553</v>
+      </c>
+      <c r="F28" t="s">
+        <v>554</v>
+      </c>
+      <c r="G28" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="29" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E29" t="str">
+        <f>"eu_"&amp;F29</f>
+        <v>eu_Ships</v>
+      </c>
+      <c r="F29" t="s">
+        <v>556</v>
+      </c>
+      <c r="G29" t="s">
+        <v>49</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="30" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E30" t="s">
+        <v>558</v>
+      </c>
+      <c r="F30" t="s">
+        <v>559</v>
+      </c>
+      <c r="G30" t="s">
+        <v>49</v>
+      </c>
+      <c r="J30" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="31" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E31" t="s">
+        <v>561</v>
+      </c>
+      <c r="F31" t="s">
+        <v>562</v>
+      </c>
+      <c r="G31" t="s">
+        <v>49</v>
+      </c>
+      <c r="J31" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="32" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E32" t="str">
+        <f>"eu_"&amp;F32</f>
+        <v>eu_Trucks</v>
+      </c>
+      <c r="F32" t="s">
+        <v>564</v>
+      </c>
+      <c r="G32" t="s">
+        <v>49</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="33" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E33" t="s">
+        <v>566</v>
+      </c>
+      <c r="F33" t="s">
+        <v>567</v>
+      </c>
+      <c r="G33" t="s">
+        <v>49</v>
+      </c>
+      <c r="J33" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="34" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E34" t="s">
+        <v>569</v>
+      </c>
+      <c r="F34" t="s">
+        <v>570</v>
+      </c>
+      <c r="G34" t="s">
+        <v>49</v>
+      </c>
+      <c r="J34" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="35" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E35" t="s">
+        <v>572</v>
+      </c>
+      <c r="F35" t="s">
+        <v>573</v>
+      </c>
+      <c r="G35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H35" t="s">
+        <v>574</v>
+      </c>
+      <c r="I35" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="36" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E36" t="s">
+        <v>576</v>
+      </c>
+      <c r="F36" t="s">
+        <v>577</v>
+      </c>
+      <c r="G36" t="s">
+        <v>49</v>
+      </c>
+      <c r="J36" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="37" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E37" t="s">
+        <v>579</v>
+      </c>
+      <c r="F37" t="s">
+        <v>580</v>
+      </c>
+      <c r="G37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H37" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="38" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E38" t="s">
+        <v>582</v>
+      </c>
+      <c r="F38" t="s">
+        <v>583</v>
+      </c>
+      <c r="G38" t="s">
+        <v>49</v>
+      </c>
+      <c r="K38" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="39" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E39" t="s">
+        <v>585</v>
+      </c>
+      <c r="F39" t="s">
+        <v>586</v>
+      </c>
+      <c r="G39" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="40" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E40" t="s">
+        <v>588</v>
+      </c>
+      <c r="F40" t="s">
+        <v>589</v>
+      </c>
+      <c r="G40" t="s">
+        <v>47</v>
+      </c>
+      <c r="H40" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="41" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E41" t="s">
+        <v>591</v>
+      </c>
+      <c r="F41" t="s">
+        <v>592</v>
+      </c>
+      <c r="G41" t="s">
+        <v>47</v>
+      </c>
+      <c r="H41" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="42" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E42" t="s">
+        <v>594</v>
+      </c>
+      <c r="F42" t="s">
+        <v>595</v>
+      </c>
+      <c r="G42" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="43" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E43" t="s">
+        <v>597</v>
+      </c>
+      <c r="F43" t="s">
+        <v>598</v>
+      </c>
+      <c r="G43" t="s">
+        <v>69</v>
+      </c>
+      <c r="H43" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="44" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E44" t="s">
+        <v>600</v>
+      </c>
+      <c r="F44" t="s">
+        <v>601</v>
+      </c>
+      <c r="G44" t="s">
+        <v>49</v>
+      </c>
+      <c r="J44" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="45" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E45" t="s">
+        <v>603</v>
+      </c>
+      <c r="F45" t="s">
+        <v>604</v>
+      </c>
+      <c r="G45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E46" t="s">
+        <v>605</v>
+      </c>
+      <c r="F46" t="s">
+        <v>606</v>
+      </c>
+      <c r="G46" t="s">
+        <v>49</v>
+      </c>
+      <c r="J46" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="47" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E47" t="str">
+        <f>"ss_"&amp;SUBSTITUTE(F47," ","")</f>
+        <v>ss_Attached</v>
+      </c>
+      <c r="F47" t="s">
+        <v>608</v>
+      </c>
+      <c r="G47" t="s">
+        <v>49</v>
+      </c>
+      <c r="J47" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="48" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="E48" t="s">
+        <v>610</v>
+      </c>
+      <c r="F48" t="s">
+        <v>611</v>
+      </c>
+      <c r="G48" t="s">
+        <v>49</v>
+      </c>
+      <c r="H48" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="49" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E49" t="s">
+        <v>613</v>
+      </c>
+      <c r="F49" t="s">
+        <v>614</v>
+      </c>
+      <c r="G49" t="s">
+        <v>49</v>
+      </c>
+      <c r="H49" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="50" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E50" t="s">
+        <v>616</v>
+      </c>
+      <c r="F50" t="s">
+        <v>617</v>
+      </c>
+      <c r="G50" t="s">
+        <v>49</v>
+      </c>
+      <c r="H50" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="51" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E51" t="str">
+        <f>"ss_"&amp;SUBSTITUTE(F51," ","")</f>
+        <v>ss_DairyCattleFarming</v>
+      </c>
+      <c r="F51" t="s">
+        <v>619</v>
+      </c>
+      <c r="G51" t="s">
+        <v>49</v>
+      </c>
+      <c r="J51" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="52" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E52" t="str">
+        <f>"ss_"&amp;SUBSTITUTE(F52," ","")</f>
+        <v>ss_Detached</v>
+      </c>
+      <c r="F52" t="s">
+        <v>621</v>
+      </c>
+      <c r="G52" t="s">
+        <v>49</v>
+      </c>
+      <c r="J52" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="53" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E53" t="str">
+        <f>"ss_"&amp;SUBSTITUTE(F53," ","")</f>
+        <v>ss_Education</v>
+      </c>
+      <c r="F53" t="s">
+        <v>623</v>
+      </c>
+      <c r="G53" t="s">
+        <v>49</v>
+      </c>
+      <c r="J53" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="54" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E54" t="str">
+        <f>"ss_"&amp;SUBSTITUTE(F54," ","")</f>
+        <v>ss_Fishing</v>
+      </c>
+      <c r="F54" t="s">
+        <v>625</v>
+      </c>
+      <c r="G54" t="s">
+        <v>49</v>
+      </c>
+      <c r="J54" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="55" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E55" t="s">
+        <v>627</v>
+      </c>
+      <c r="F55" t="s">
+        <v>628</v>
+      </c>
+      <c r="G55" t="s">
+        <v>49</v>
+      </c>
+      <c r="H55" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="56" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E56" t="str">
+        <f t="shared" ref="E56:E69" si="1">"ss_"&amp;SUBSTITUTE(F56," ","")</f>
+        <v>ss_Forestry</v>
+      </c>
+      <c r="F56" t="s">
+        <v>630</v>
+      </c>
+      <c r="G56" t="s">
+        <v>49</v>
+      </c>
+      <c r="J56" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="57" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E57" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Healthcare</v>
+      </c>
+      <c r="F57" t="s">
+        <v>632</v>
+      </c>
+      <c r="G57" t="s">
+        <v>49</v>
+      </c>
+      <c r="J57" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="58" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E58" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Horticulture</v>
+      </c>
+      <c r="F58" t="s">
+        <v>634</v>
+      </c>
+      <c r="G58" t="s">
+        <v>49</v>
+      </c>
+      <c r="J58" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="59" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E59" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Indoorcropping</v>
+      </c>
+      <c r="F59" t="s">
+        <v>636</v>
+      </c>
+      <c r="G59" t="s">
+        <v>49</v>
+      </c>
+      <c r="J59" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="60" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E60" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Livestock</v>
+      </c>
+      <c r="F60" t="s">
+        <v>638</v>
+      </c>
+      <c r="G60" t="s">
+        <v>49</v>
+      </c>
+      <c r="J60" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="61" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E61" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Meat</v>
+      </c>
+      <c r="F61" t="s">
+        <v>640</v>
+      </c>
+      <c r="G61" t="s">
+        <v>49</v>
+      </c>
+      <c r="H61" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="62" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E62" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Metals</v>
+      </c>
+      <c r="F62" t="s">
+        <v>642</v>
+      </c>
+      <c r="G62" t="s">
+        <v>49</v>
+      </c>
+      <c r="H62" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="63" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E63" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Methanol</v>
+      </c>
+      <c r="F63" t="s">
+        <v>644</v>
+      </c>
+      <c r="G63" t="s">
+        <v>49</v>
+      </c>
+      <c r="H63" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="64" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E64" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Minerals</v>
+      </c>
+      <c r="F64" t="s">
+        <v>646</v>
+      </c>
+      <c r="G64" t="s">
+        <v>49</v>
+      </c>
+      <c r="H64" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="65" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E65" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Mining</v>
+      </c>
+      <c r="F65" t="s">
+        <v>648</v>
+      </c>
+      <c r="G65" t="s">
+        <v>49</v>
+      </c>
+      <c r="H65" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="66" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E66" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_Office</v>
+      </c>
+      <c r="F66" t="s">
+        <v>650</v>
+      </c>
+      <c r="G66" t="s">
+        <v>49</v>
+      </c>
+      <c r="J66" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="67" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E67" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_OtherInd</v>
+      </c>
+      <c r="F67" t="s">
+        <v>652</v>
+      </c>
+      <c r="G67" t="s">
+        <v>49</v>
+      </c>
+      <c r="H67" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="68" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E68" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_OtherAgri</v>
+      </c>
+      <c r="F68" t="s">
+        <v>654</v>
+      </c>
+      <c r="G68" t="s">
+        <v>49</v>
+      </c>
+      <c r="J68" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="69" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E69" t="str">
+        <f t="shared" si="1"/>
+        <v>ss_OtherCom</v>
+      </c>
+      <c r="F69" t="s">
+        <v>656</v>
+      </c>
+      <c r="G69" t="s">
+        <v>49</v>
+      </c>
+      <c r="J69" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="70" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E70" t="s">
+        <v>658</v>
+      </c>
+      <c r="F70" t="s">
+        <v>659</v>
+      </c>
+      <c r="G70" t="s">
+        <v>49</v>
+      </c>
+      <c r="H70" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="71" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E71" t="str">
+        <f>"ss_"&amp;SUBSTITUTE(F71," ","")</f>
+        <v>ss_Refining</v>
+      </c>
+      <c r="F71" t="s">
+        <v>661</v>
+      </c>
+      <c r="G71" t="s">
+        <v>49</v>
+      </c>
+      <c r="H71" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="72" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E72" t="s">
+        <v>663</v>
+      </c>
+      <c r="F72" t="s">
+        <v>664</v>
+      </c>
+      <c r="G72" t="s">
+        <v>49</v>
+      </c>
+      <c r="H72" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="73" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E73" t="str">
+        <f>"ss_"&amp;SUBSTITUTE(F73," ","")</f>
+        <v>ss_Urea</v>
+      </c>
+      <c r="F73" t="s">
+        <v>666</v>
+      </c>
+      <c r="G73" t="s">
+        <v>49</v>
+      </c>
+      <c r="H73" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="74" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E74" t="str">
+        <f>"ss_"&amp;SUBSTITUTE(F74," ","")</f>
+        <v>ss_WoodProdMfg</v>
+      </c>
+      <c r="F74" t="s">
+        <v>668</v>
+      </c>
+      <c r="G74" t="s">
+        <v>49</v>
+      </c>
+      <c r="H74" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="75" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E75" t="str">
+        <f>"ss_"&amp;SUBSTITUTE(F75," ","")</f>
+        <v>ss_WSR</v>
+      </c>
+      <c r="F75" t="s">
+        <v>670</v>
+      </c>
+      <c r="G75" t="s">
+        <v>49</v>
+      </c>
+      <c r="J75" t="s">
+        <v>671</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F3D05A-3957-4820-93DE-DB11637970DC}">
+  <dimension ref="A1:O44"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="35.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E2" t="s">
+        <v>675</v>
+      </c>
+      <c r="F2" t="s">
+        <v>676</v>
+      </c>
+      <c r="G2" t="s">
+        <v>677</v>
+      </c>
+      <c r="H2" t="s">
+        <v>678</v>
+      </c>
+      <c r="I2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A3" t="str">
+        <f>"nrg_"&amp;N3</f>
+        <v>nrg_COA</v>
+      </c>
+      <c r="B3" t="str">
+        <f>O3</f>
+        <v>Coal</v>
+      </c>
+      <c r="C3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D3" t="str">
+        <f>"*"&amp;N3</f>
+        <v>*COA</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A4" t="str">
+        <f t="shared" ref="A4:A39" si="0">"nrg_"&amp;N4</f>
+        <v>nrg_DSL</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" ref="B4:B39" si="1">O4</f>
+        <v>Diesel</v>
+      </c>
+      <c r="C4" t="s">
+        <v>680</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" ref="D4:D39" si="2">"*"&amp;N4</f>
+        <v>*DSL</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_ELC</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">Electricity </v>
+      </c>
+      <c r="C5" t="s">
+        <v>680</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="2"/>
+        <v>*ELC</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_FOL</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="1"/>
+        <v>Fuel Oil</v>
+      </c>
+      <c r="C6" t="s">
+        <v>680</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="2"/>
+        <v>*FOL</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_GEO</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="1"/>
+        <v>Geothermal</v>
+      </c>
+      <c r="C7" t="s">
+        <v>680</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="2"/>
+        <v>*GEO</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A8" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_H2R</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="1"/>
+        <v>Hydrogen</v>
+      </c>
+      <c r="C8" t="s">
+        <v>680</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="2"/>
+        <v>*H2R</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A9" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_LPG</v>
+      </c>
+      <c r="B9" t="str">
+        <f t="shared" si="1"/>
+        <v>LPG</v>
+      </c>
+      <c r="C9" t="s">
+        <v>680</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="2"/>
+        <v>*LPG</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A10" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_NGA</v>
+      </c>
+      <c r="B10" t="str">
+        <f t="shared" si="1"/>
+        <v>Natural Gas</v>
+      </c>
+      <c r="C10" t="s">
+        <v>680</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="2"/>
+        <v>*NGA</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A11" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_PET</v>
+      </c>
+      <c r="B11" t="str">
+        <f t="shared" si="1"/>
+        <v>Petrol</v>
+      </c>
+      <c r="C11" t="s">
+        <v>680</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="2"/>
+        <v>*PET</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A12" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_PLT</v>
+      </c>
+      <c r="B12" t="str">
+        <f t="shared" si="1"/>
+        <v>Pellet</v>
+      </c>
+      <c r="C12" t="s">
+        <v>680</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="2"/>
+        <v>*PLT</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A13" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_WOD</v>
+      </c>
+      <c r="B13" t="str">
+        <f t="shared" si="1"/>
+        <v>Wood</v>
+      </c>
+      <c r="C13" t="s">
+        <v>680</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="2"/>
+        <v>*WOD</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A14" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_WST</v>
+      </c>
+      <c r="B14" t="str">
+        <f t="shared" si="1"/>
+        <v>Waste</v>
+      </c>
+      <c r="C14" t="s">
+        <v>680</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="2"/>
+        <v>*WST</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A15" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_MNR</v>
+      </c>
+      <c r="B15" t="str">
+        <f t="shared" si="1"/>
+        <v>Manure</v>
+      </c>
+      <c r="C15" t="s">
+        <v>680</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="2"/>
+        <v>*MNR</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A16" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_BIG</v>
+      </c>
+      <c r="B16" t="str">
+        <f t="shared" si="1"/>
+        <v>Biogas</v>
+      </c>
+      <c r="C16" t="s">
+        <v>680</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="2"/>
+        <v>*BIG</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A17" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_BIL</v>
+      </c>
+      <c r="B17" t="str">
+        <f t="shared" si="1"/>
+        <v>Bioliquid</v>
+      </c>
+      <c r="C17" t="s">
+        <v>680</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="2"/>
+        <v>*BIL</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A18" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_COL</v>
+      </c>
+      <c r="B18" t="str">
+        <f t="shared" si="1"/>
+        <v>Lignite</v>
+      </c>
+      <c r="C18" t="s">
+        <v>680</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="2"/>
+        <v>*COL</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A19" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_seq</v>
+      </c>
+      <c r="B19" t="str">
+        <f t="shared" si="1"/>
+        <v>CO2 to CCS</v>
+      </c>
+      <c r="C19" t="s">
+        <v>680</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="2"/>
+        <v>*seq</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A20" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_CO2</v>
+      </c>
+      <c r="B20" t="str">
+        <f t="shared" si="1"/>
+        <v>CO2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>680</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="2"/>
+        <v>*CO2</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A21" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_DID</v>
+      </c>
+      <c r="B21" t="str">
+        <f t="shared" si="1"/>
+        <v>Drop-In Diesel</v>
+      </c>
+      <c r="C21" t="s">
+        <v>680</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="2"/>
+        <v>*DID</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A22" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_DIJ</v>
+      </c>
+      <c r="B22" t="str">
+        <f t="shared" si="1"/>
+        <v>Drop-In Jet</v>
+      </c>
+      <c r="C22" t="s">
+        <v>680</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="2"/>
+        <v>*DIJ</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A23" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_LCD</v>
+      </c>
+      <c r="B23" t="str">
+        <f t="shared" si="1"/>
+        <v>Electricity Production</v>
+      </c>
+      <c r="C23" t="s">
+        <v>680</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="2"/>
+        <v>*LCD</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A24" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_CDD</v>
+      </c>
+      <c r="B24" t="str">
+        <f t="shared" si="1"/>
+        <v>Electricity Production</v>
+      </c>
+      <c r="C24" t="s">
+        <v>680</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="2"/>
+        <v>*CDD</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A25" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_-HV</v>
+      </c>
+      <c r="B25" t="str">
+        <f t="shared" si="1"/>
+        <v>Electricity Production</v>
+      </c>
+      <c r="C25" t="s">
+        <v>680</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="2"/>
+        <v>*-HV</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A26" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_HYD</v>
+      </c>
+      <c r="B26" t="str">
+        <f t="shared" si="1"/>
+        <v>Hydro</v>
+      </c>
+      <c r="C26" t="s">
+        <v>680</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="2"/>
+        <v>*HYD</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A27" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_-MV</v>
+      </c>
+      <c r="B27" t="str">
+        <f t="shared" si="1"/>
+        <v>Electricity Production</v>
+      </c>
+      <c r="C27" t="s">
+        <v>680</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="2"/>
+        <v>*-MV</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A28" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_OIL</v>
+      </c>
+      <c r="B28" t="str">
+        <f t="shared" si="1"/>
+        <v>Oil</v>
+      </c>
+      <c r="C28" t="s">
+        <v>680</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="2"/>
+        <v>*OIL</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A29" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_SOL</v>
+      </c>
+      <c r="B29" t="str">
+        <f t="shared" si="1"/>
+        <v>Solar</v>
+      </c>
+      <c r="C29" t="s">
+        <v>680</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="2"/>
+        <v>*SOL</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A30" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_TID</v>
+      </c>
+      <c r="B30" t="str">
+        <f t="shared" si="1"/>
+        <v>Tidal</v>
+      </c>
+      <c r="C30" t="s">
+        <v>680</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="2"/>
+        <v>*TID</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A31" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_URN</v>
+      </c>
+      <c r="B31" t="str">
+        <f t="shared" si="1"/>
+        <v>Uranium</v>
+      </c>
+      <c r="C31" t="s">
+        <v>680</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="2"/>
+        <v>*URN</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A32" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_WIN</v>
+      </c>
+      <c r="B32" t="str">
+        <f t="shared" si="1"/>
+        <v>Wind</v>
+      </c>
+      <c r="C32" t="s">
+        <v>680</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" si="2"/>
+        <v>*WIN</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A33" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_H2C</v>
+      </c>
+      <c r="B33" t="str">
+        <f t="shared" si="1"/>
+        <v>Green Hydrogen Green Hydrogen Fuel</v>
+      </c>
+      <c r="C33" t="s">
+        <v>680</v>
+      </c>
+      <c r="D33" t="str">
+        <f t="shared" si="2"/>
+        <v>*H2C</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>727</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A34" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_H2D</v>
+      </c>
+      <c r="B34" t="str">
+        <f t="shared" si="1"/>
+        <v>Green Hydrogen Green Hydrogen Fuel</v>
+      </c>
+      <c r="C34" t="s">
+        <v>680</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" si="2"/>
+        <v>*H2D</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A35" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_JET</v>
+      </c>
+      <c r="B35" t="str">
+        <f t="shared" si="1"/>
+        <v>Jet Fuel</v>
+      </c>
+      <c r="C35" t="s">
+        <v>680</v>
+      </c>
+      <c r="D35" t="str">
+        <f t="shared" si="2"/>
+        <v>*JET</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A36" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_LNG</v>
+      </c>
+      <c r="B36" t="str">
+        <f t="shared" si="1"/>
+        <v>LNG</v>
+      </c>
+      <c r="C36" t="s">
+        <v>680</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="2"/>
+        <v>*LNG</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A37" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_ILD</v>
+      </c>
+      <c r="B37" t="str">
+        <f t="shared" si="1"/>
+        <v>Crude Oil (domestic)</v>
+      </c>
+      <c r="C37" t="s">
+        <v>680</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="2"/>
+        <v>*ILD</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A38" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_ILI</v>
+      </c>
+      <c r="B38" t="str">
+        <f t="shared" si="1"/>
+        <v>Crude Oil (imported)</v>
+      </c>
+      <c r="C38" t="s">
+        <v>680</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="2"/>
+        <v>*ILI</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A39" t="str">
+        <f t="shared" si="0"/>
+        <v>nrg_OTH</v>
+      </c>
+      <c r="B39" t="str">
+        <f t="shared" si="1"/>
+        <v>Other Oil</v>
+      </c>
+      <c r="C39" t="s">
+        <v>680</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" si="2"/>
+        <v>*OTH</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A40" t="str">
+        <f>"dem_"&amp;N40</f>
+        <v>dem_agriculture</v>
+      </c>
+      <c r="B40" t="str">
+        <f>N40</f>
+        <v>agriculture</v>
+      </c>
+      <c r="C40" t="s">
+        <v>739</v>
+      </c>
+      <c r="D40" t="str">
+        <f>O40</f>
+        <v>A*,meat*,D*</v>
+      </c>
+      <c r="N40" t="s">
+        <v>740</v>
+      </c>
+      <c r="O40" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A41" t="str">
+        <f>"dem_"&amp;N41</f>
+        <v>dem_commercial</v>
+      </c>
+      <c r="B41" t="str">
+        <f>N41</f>
+        <v>commercial</v>
+      </c>
+      <c r="C41" t="s">
+        <v>739</v>
+      </c>
+      <c r="D41" t="str">
+        <f>O41</f>
+        <v>C*</v>
+      </c>
+      <c r="N41" t="s">
+        <v>742</v>
+      </c>
+      <c r="O41" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A42" t="str">
+        <f>"dem_"&amp;N42</f>
+        <v>dem_industry</v>
+      </c>
+      <c r="B42" t="str">
+        <f>N42</f>
+        <v>industry</v>
+      </c>
+      <c r="C42" t="s">
+        <v>739</v>
+      </c>
+      <c r="D42" t="str">
+        <f>O42</f>
+        <v>F*,I*,ref*,M*,-meat*,O*,P*,U*,W*</v>
+      </c>
+      <c r="N42" t="s">
+        <v>63</v>
+      </c>
+      <c r="O42" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A43" t="str">
+        <f>"dem_"&amp;N43</f>
+        <v>dem_residential</v>
+      </c>
+      <c r="B43" t="str">
+        <f>N43</f>
+        <v>residential</v>
+      </c>
+      <c r="C43" t="s">
+        <v>739</v>
+      </c>
+      <c r="D43" t="str">
+        <f>O43</f>
+        <v>R*,-ref*</v>
+      </c>
+      <c r="N43" t="s">
+        <v>745</v>
+      </c>
+      <c r="O43" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A44" t="str">
+        <f>"dem_"&amp;N44</f>
+        <v>dem_transport</v>
+      </c>
+      <c r="B44" t="str">
+        <f>N44</f>
+        <v>transport</v>
+      </c>
+      <c r="C44" t="s">
+        <v>739</v>
+      </c>
+      <c r="D44" t="str">
+        <f>O44</f>
+        <v>T*</v>
+      </c>
+      <c r="N44" t="s">
+        <v>64</v>
+      </c>
+      <c r="O44" t="s">
+        <v>747</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sets-vervestacks.xlsx
+++ b/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D317B803-F8B8-4CD7-BB8E-98CBBF2C7720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDC9771-0CBF-4708-84CB-1E8AFEA4BDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="757">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -2287,6 +2287,33 @@
   </si>
   <si>
     <t>T*</t>
+  </si>
+  <si>
+    <t>sect_commercial</t>
+  </si>
+  <si>
+    <t>COM*</t>
+  </si>
+  <si>
+    <t>sect_residential</t>
+  </si>
+  <si>
+    <t>RES*</t>
+  </si>
+  <si>
+    <t>sect_industry</t>
+  </si>
+  <si>
+    <t>sect_agriculture</t>
+  </si>
+  <si>
+    <t>AGR*</t>
+  </si>
+  <si>
+    <t>sect_transport</t>
+  </si>
+  <si>
+    <t>TRA*</t>
   </si>
 </sst>
 </file>
@@ -7554,7 +7581,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F3D05A-3957-4820-93DE-DB11637970DC}">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="35.3984375" bestFit="1" customWidth="1"/>
@@ -8560,6 +8587,61 @@
         <v>747</v>
       </c>
     </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>748</v>
+      </c>
+      <c r="B45" t="s">
+        <v>742</v>
+      </c>
+      <c r="D45" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>750</v>
+      </c>
+      <c r="B46" t="s">
+        <v>745</v>
+      </c>
+      <c r="D46" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>752</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+      <c r="D47" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>753</v>
+      </c>
+      <c r="B48" t="s">
+        <v>740</v>
+      </c>
+      <c r="D48" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>755</v>
+      </c>
+      <c r="B49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D49" t="s">
+        <v>756</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sets-vervestacks.xlsx
+++ b/Sets-vervestacks.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,20 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDC9771-0CBF-4708-84CB-1E8AFEA4BDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
-    <sheet name="geo_sets" sheetId="3" r:id="rId2"/>
-    <sheet name="VEDA_Sets-Proc" sheetId="1" r:id="rId3"/>
-    <sheet name="SetsEditor- Proc" sheetId="4" r:id="rId4"/>
-    <sheet name="SetsEditor- Comm" sheetId="5" r:id="rId5"/>
+    <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId3"/>
+    <sheet name="geo_sets" sheetId="3" r:id="rId4"/>
+    <sheet name="VEDA_Sets-Proc" sheetId="1" r:id="rId5"/>
+    <sheet name="SetsEditor- Proc" sheetId="4" r:id="rId6"/>
+    <sheet name="SetsEditor- Comm" sheetId="5" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SetsEditor- Proc'!$D$2:$F$75</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="762">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -1866,7 +1863,7 @@
     <t>Transport</t>
   </si>
   <si>
-    <t>T[_]*</t>
+    <t>T[_]*,elc_road*</t>
   </si>
   <si>
     <t>Attached</t>
@@ -2313,20 +2310,41 @@
     <t>sect_transport</t>
   </si>
   <si>
-    <t>TRA*</t>
+    <t>TRA*,elc_road*</t>
+  </si>
+  <si>
+    <t>-ev*</t>
+  </si>
+  <si>
+    <t>-IRE</t>
+  </si>
+  <si>
+    <t>nrg_ELC</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>*ELC,elc_road*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2379,42 +2397,134 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color theme="4" tint="0.49995422223578601"/>
+        <color theme="4" tint="0.499949991703033"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399980008602142"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="20"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="21"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="22"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
-    <cellStyle name="Neutral 2" xfId="3" xr:uid="{599912E3-8559-451E-9420-BD3F24E264C7}"/>
+  <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Heading 2" xfId="20" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="21" builtinId="18"/>
+    <cellStyle name="Neutral 2" xfId="22"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2722,27 +2832,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB068F12-506D-4B74-BF24-03EBDA23C84D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB068F12-506D-4B74-BF24-03EBDA23C84D}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.53125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.57142857142857" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.57142857142857" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85714285714286" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42857142857143" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.71428571428571" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="14.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="14.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2768,22 +2878,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:11" ht="14.25">
       <c r="B3" t="str">
         <f>"e_*"&amp;K3</f>
         <v>e_*220</v>
       </c>
       <c r="D3" t="str">
-        <f t="shared" ref="D3:D23" si="0">"Elec-"&amp;K3&amp;"V"</f>
+        <f t="shared" si="0" ref="D3:D23">"Elec-"&amp;K3&amp;"V"</f>
         <v>Elec-220V</v>
       </c>
       <c r="K3">
         <v>220</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:11" ht="14.25">
       <c r="B4" t="str">
-        <f t="shared" ref="B4:B23" si="1">"e_*"&amp;K4</f>
+        <f t="shared" si="1" ref="B4:B23">"e_*"&amp;K4</f>
         <v>e_*400</v>
       </c>
       <c r="D4" t="str">
@@ -2794,7 +2904,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:11" ht="14.25">
       <c r="B5" t="str">
         <f t="shared" si="1"/>
         <v>e_*380</v>
@@ -2807,7 +2917,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:11" ht="14.25">
       <c r="B6" t="str">
         <f t="shared" si="1"/>
         <v>e_*225</v>
@@ -2820,7 +2930,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:11" ht="14.25">
       <c r="B7" t="str">
         <f t="shared" si="1"/>
         <v>e_*330</v>
@@ -2833,7 +2943,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:11" ht="14.25">
       <c r="B8" t="str">
         <f t="shared" si="1"/>
         <v>e_*275</v>
@@ -2846,7 +2956,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:11" ht="14.25">
       <c r="B9" t="str">
         <f t="shared" si="1"/>
         <v>e_*420</v>
@@ -2859,7 +2969,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:11" ht="14.25">
       <c r="B10" t="str">
         <f t="shared" si="1"/>
         <v>e_*300</v>
@@ -2872,7 +2982,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:11" ht="14.25">
       <c r="B11" t="str">
         <f t="shared" si="1"/>
         <v>e_*500</v>
@@ -2885,7 +2995,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:11" ht="14.25">
       <c r="B12" t="str">
         <f t="shared" si="1"/>
         <v>e_*750</v>
@@ -2898,7 +3008,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:11" ht="14.25">
       <c r="B13" t="str">
         <f t="shared" si="1"/>
         <v>e_*450</v>
@@ -2911,7 +3021,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:11" ht="14.25">
       <c r="B14" t="str">
         <f t="shared" si="1"/>
         <v>e_*515</v>
@@ -2924,7 +3034,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:11" ht="14.25">
       <c r="B15" t="str">
         <f t="shared" si="1"/>
         <v>e_*525</v>
@@ -2937,7 +3047,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:11" ht="14.25">
       <c r="B16" t="str">
         <f t="shared" si="1"/>
         <v>e_*320</v>
@@ -2950,7 +3060,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:11" ht="14.25">
       <c r="B17" t="str">
         <f t="shared" si="1"/>
         <v>e_*150</v>
@@ -2963,7 +3073,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:11" ht="14.25">
       <c r="B18" t="str">
         <f t="shared" si="1"/>
         <v>e_*270</v>
@@ -2976,7 +3086,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:11" ht="14.25">
       <c r="B19" t="str">
         <f t="shared" si="1"/>
         <v>e_*350</v>
@@ -2989,7 +3099,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:11" ht="14.25">
       <c r="B20" t="str">
         <f t="shared" si="1"/>
         <v>e_*250</v>
@@ -3002,7 +3112,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:11" ht="14.25">
       <c r="B21" t="str">
         <f t="shared" si="1"/>
         <v>e_*200</v>
@@ -3015,7 +3125,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:11" ht="14.25">
       <c r="B22" t="str">
         <f t="shared" si="1"/>
         <v>e_*236</v>
@@ -3028,7 +3138,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:11" ht="14.25">
       <c r="B23" t="str">
         <f t="shared" si="1"/>
         <v>e_*600</v>
@@ -3041,7 +3151,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:4" ht="14.25">
       <c r="B24" t="s">
         <v>51</v>
       </c>
@@ -3049,7 +3159,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:4" ht="14.25">
       <c r="B25" t="s">
         <v>52</v>
       </c>
@@ -3057,7 +3167,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:4" ht="14.25">
       <c r="B26" t="s">
         <v>67</v>
       </c>
@@ -3065,7 +3175,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:4" ht="14.25">
       <c r="B27" t="s">
         <v>68</v>
       </c>
@@ -3073,7 +3183,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:4" ht="14.25">
       <c r="B28" t="s">
         <v>53</v>
       </c>
@@ -3082,7 +3192,7 @@
         <v>bioenergy</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:4" ht="14.25">
       <c r="B29" t="s">
         <v>54</v>
       </c>
@@ -3091,7 +3201,7 @@
         <v>hydrogen</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:4" ht="14.25">
       <c r="B30" t="s">
         <v>43</v>
       </c>
@@ -3100,7 +3210,7 @@
         <v>nuclear</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:4" ht="14.25">
       <c r="B31" t="s">
         <v>55</v>
       </c>
@@ -3109,7 +3219,7 @@
         <v>ELC</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:4" ht="14.25">
       <c r="B32" t="s">
         <v>56</v>
       </c>
@@ -3117,7 +3227,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:4" ht="14.25">
       <c r="B33" t="s">
         <v>57</v>
       </c>
@@ -3125,7 +3235,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:4" ht="14.25">
       <c r="B34" t="s">
         <v>58</v>
       </c>
@@ -3133,7 +3243,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:4" ht="14.25">
       <c r="B35" t="s">
         <v>59</v>
       </c>
@@ -3141,7 +3251,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:4" ht="14.25">
       <c r="B36" t="s">
         <v>60</v>
       </c>
@@ -3150,7 +3260,7 @@
         <v>co2</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:4" ht="14.25">
       <c r="B37" t="s">
         <v>61</v>
       </c>
@@ -3160,29 +3270,29 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A26:D37">
-    <sortCondition ref="A26:A37"/>
+  <sortState ref="A26:D37">
+    <sortCondition sortBy="value" ref="A26:A37"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB38C7C-36FF-4DE0-9337-A7E9284495EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB38C7C-36FF-4DE0-9337-A7E9284495EF}">
   <dimension ref="B9:E200"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1428571428571" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5714285714286" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:2" ht="14.25">
       <c r="B9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:5" ht="14.25">
       <c r="B10" t="s">
         <v>99</v>
       </c>
@@ -3196,7 +3306,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:5" ht="14.25">
       <c r="B11" t="s">
         <v>103</v>
       </c>
@@ -3210,7 +3320,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:5" ht="14.25">
       <c r="B12" t="s">
         <v>106</v>
       </c>
@@ -3224,7 +3334,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:5" ht="14.25">
       <c r="B13" t="s">
         <v>108</v>
       </c>
@@ -3238,7 +3348,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:5" ht="14.25">
       <c r="B14" t="s">
         <v>110</v>
       </c>
@@ -3252,7 +3362,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:5" ht="14.25">
       <c r="B15" t="s">
         <v>112</v>
       </c>
@@ -3266,7 +3376,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:5" ht="14.25">
       <c r="B16" t="s">
         <v>114</v>
       </c>
@@ -3280,7 +3390,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:5" ht="14.25">
       <c r="B17" t="s">
         <v>116</v>
       </c>
@@ -3294,7 +3404,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:5" ht="14.25">
       <c r="B18" t="s">
         <v>118</v>
       </c>
@@ -3308,7 +3418,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:5" ht="14.25">
       <c r="B19" t="s">
         <v>120</v>
       </c>
@@ -3322,7 +3432,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:5" ht="14.25">
       <c r="B20" t="s">
         <v>122</v>
       </c>
@@ -3336,7 +3446,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:5" ht="14.25">
       <c r="B21" t="s">
         <v>124</v>
       </c>
@@ -3350,7 +3460,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:5" ht="14.25">
       <c r="B22" t="s">
         <v>126</v>
       </c>
@@ -3364,7 +3474,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:5" ht="14.25">
       <c r="B23" t="s">
         <v>128</v>
       </c>
@@ -3378,7 +3488,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:5" ht="14.25">
       <c r="B24" t="s">
         <v>130</v>
       </c>
@@ -3392,7 +3502,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:5" ht="14.25">
       <c r="B25" t="s">
         <v>132</v>
       </c>
@@ -3406,7 +3516,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:5" ht="14.25">
       <c r="B26" t="s">
         <v>134</v>
       </c>
@@ -3420,7 +3530,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:5" ht="14.25">
       <c r="B27" t="s">
         <v>136</v>
       </c>
@@ -3434,7 +3544,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:5" ht="14.25">
       <c r="B28" t="s">
         <v>138</v>
       </c>
@@ -3448,7 +3558,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:5" ht="14.25">
       <c r="B29" t="s">
         <v>140</v>
       </c>
@@ -3462,7 +3572,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:5" ht="14.25">
       <c r="B30" t="s">
         <v>142</v>
       </c>
@@ -3476,7 +3586,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:5" ht="14.25">
       <c r="B31" t="s">
         <v>144</v>
       </c>
@@ -3490,7 +3600,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:5" ht="14.25">
       <c r="B32" t="s">
         <v>146</v>
       </c>
@@ -3504,7 +3614,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" ht="14.25">
       <c r="B33" t="s">
         <v>148</v>
       </c>
@@ -3518,7 +3628,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" ht="14.25">
       <c r="B34" t="s">
         <v>150</v>
       </c>
@@ -3532,7 +3642,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" ht="14.25">
       <c r="B35" t="s">
         <v>152</v>
       </c>
@@ -3546,7 +3656,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" ht="14.25">
       <c r="B36" t="s">
         <v>154</v>
       </c>
@@ -3560,7 +3670,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:5" ht="14.25">
       <c r="B37" t="s">
         <v>156</v>
       </c>
@@ -3574,7 +3684,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:5" ht="14.25">
       <c r="B38" t="s">
         <v>158</v>
       </c>
@@ -3588,7 +3698,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:5" ht="14.25">
       <c r="B39" t="s">
         <v>160</v>
       </c>
@@ -3602,7 +3712,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:5" ht="14.25">
       <c r="B40" t="s">
         <v>162</v>
       </c>
@@ -3616,7 +3726,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:5" ht="14.25">
       <c r="B41" t="s">
         <v>164</v>
       </c>
@@ -3630,7 +3740,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:5" ht="14.25">
       <c r="B42" t="s">
         <v>166</v>
       </c>
@@ -3644,7 +3754,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:5" ht="14.25">
       <c r="B43" t="s">
         <v>168</v>
       </c>
@@ -3658,7 +3768,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:5" ht="14.25">
       <c r="B44" t="s">
         <v>170</v>
       </c>
@@ -3672,7 +3782,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:5" ht="14.25">
       <c r="B45" t="s">
         <v>172</v>
       </c>
@@ -3686,7 +3796,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:5" ht="14.25">
       <c r="B46" t="s">
         <v>174</v>
       </c>
@@ -3700,7 +3810,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:5" ht="14.25">
       <c r="B47" t="s">
         <v>176</v>
       </c>
@@ -3714,7 +3824,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:5" ht="14.25">
       <c r="B48" t="s">
         <v>178</v>
       </c>
@@ -3728,7 +3838,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:5" ht="14.25">
       <c r="B49" t="s">
         <v>180</v>
       </c>
@@ -3742,7 +3852,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:5" ht="14.25">
       <c r="B50" t="s">
         <v>182</v>
       </c>
@@ -3756,7 +3866,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:5" ht="14.25">
       <c r="B51" t="s">
         <v>184</v>
       </c>
@@ -3770,7 +3880,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:5" ht="14.25">
       <c r="B52" t="s">
         <v>186</v>
       </c>
@@ -3784,7 +3894,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:5" ht="14.25">
       <c r="B53" t="s">
         <v>188</v>
       </c>
@@ -3798,7 +3908,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:5" ht="14.25">
       <c r="B54" t="s">
         <v>190</v>
       </c>
@@ -3812,7 +3922,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:5" ht="14.25">
       <c r="B55" t="s">
         <v>192</v>
       </c>
@@ -3826,7 +3936,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:5" ht="14.25">
       <c r="B56" t="s">
         <v>194</v>
       </c>
@@ -3840,7 +3950,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:5" ht="14.25">
       <c r="B57" t="s">
         <v>196</v>
       </c>
@@ -3854,7 +3964,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:5" ht="14.25">
       <c r="B58" t="s">
         <v>198</v>
       </c>
@@ -3868,7 +3978,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:5" ht="14.25">
       <c r="B59" t="s">
         <v>200</v>
       </c>
@@ -3882,7 +3992,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:5" ht="14.25">
       <c r="B60" t="s">
         <v>202</v>
       </c>
@@ -3896,7 +4006,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:5" ht="14.25">
       <c r="B61" t="s">
         <v>204</v>
       </c>
@@ -3910,7 +4020,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:5" ht="14.25">
       <c r="B62" t="s">
         <v>206</v>
       </c>
@@ -3924,7 +4034,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:5" ht="14.25">
       <c r="B63" t="s">
         <v>208</v>
       </c>
@@ -3938,7 +4048,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:5" ht="14.25">
       <c r="B64" t="s">
         <v>210</v>
       </c>
@@ -3952,7 +4062,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:5" ht="14.25">
       <c r="B65" t="s">
         <v>212</v>
       </c>
@@ -3966,7 +4076,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:5" ht="14.25">
       <c r="B66" t="s">
         <v>214</v>
       </c>
@@ -3980,7 +4090,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:5" ht="14.25">
       <c r="B67" t="s">
         <v>216</v>
       </c>
@@ -3994,7 +4104,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:5" ht="14.25">
       <c r="B68" t="s">
         <v>218</v>
       </c>
@@ -4008,7 +4118,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:5" ht="14.25">
       <c r="B69" t="s">
         <v>220</v>
       </c>
@@ -4022,7 +4132,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:5" ht="14.25">
       <c r="B70" t="s">
         <v>222</v>
       </c>
@@ -4036,7 +4146,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:5" ht="14.25">
       <c r="B71" t="s">
         <v>224</v>
       </c>
@@ -4050,7 +4160,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:5" ht="14.25">
       <c r="B72" t="s">
         <v>226</v>
       </c>
@@ -4064,7 +4174,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:5" ht="14.25">
       <c r="B73" t="s">
         <v>228</v>
       </c>
@@ -4078,7 +4188,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:5" ht="14.25">
       <c r="B74" t="s">
         <v>230</v>
       </c>
@@ -4092,7 +4202,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:5" ht="14.25">
       <c r="B75" t="s">
         <v>232</v>
       </c>
@@ -4106,7 +4216,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:5" ht="14.25">
       <c r="B76" t="s">
         <v>234</v>
       </c>
@@ -4120,7 +4230,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:5" ht="14.25">
       <c r="B77" t="s">
         <v>236</v>
       </c>
@@ -4134,7 +4244,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:5" ht="14.25">
       <c r="B78" t="s">
         <v>238</v>
       </c>
@@ -4148,7 +4258,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:5" ht="14.25">
       <c r="B79" t="s">
         <v>240</v>
       </c>
@@ -4162,7 +4272,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:5" ht="14.25">
       <c r="B80" t="s">
         <v>242</v>
       </c>
@@ -4176,7 +4286,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:5" ht="14.25">
       <c r="B81" t="s">
         <v>244</v>
       </c>
@@ -4190,7 +4300,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:5" ht="14.25">
       <c r="B82" t="s">
         <v>246</v>
       </c>
@@ -4204,7 +4314,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:5" ht="14.25">
       <c r="B83" t="s">
         <v>248</v>
       </c>
@@ -4218,7 +4328,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:5" ht="14.25">
       <c r="B84" t="s">
         <v>250</v>
       </c>
@@ -4232,7 +4342,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:5" ht="14.25">
       <c r="B85" t="s">
         <v>252</v>
       </c>
@@ -4246,7 +4356,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:5" ht="14.25">
       <c r="B86" t="s">
         <v>254</v>
       </c>
@@ -4260,7 +4370,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:5" ht="14.25">
       <c r="B87" t="s">
         <v>256</v>
       </c>
@@ -4274,7 +4384,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:5" ht="14.25">
       <c r="B88" t="s">
         <v>258</v>
       </c>
@@ -4288,7 +4398,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:5" ht="14.25">
       <c r="B89" t="s">
         <v>260</v>
       </c>
@@ -4302,7 +4412,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:5" ht="14.25">
       <c r="B90" t="s">
         <v>262</v>
       </c>
@@ -4316,7 +4426,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:5" ht="14.25">
       <c r="B91" t="s">
         <v>264</v>
       </c>
@@ -4330,7 +4440,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:5" ht="14.25">
       <c r="B92" t="s">
         <v>266</v>
       </c>
@@ -4344,7 +4454,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:5" ht="14.25">
       <c r="B93" t="s">
         <v>268</v>
       </c>
@@ -4358,7 +4468,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:5" ht="14.25">
       <c r="B94" t="s">
         <v>270</v>
       </c>
@@ -4372,7 +4482,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:5" ht="14.25">
       <c r="B95" t="s">
         <v>272</v>
       </c>
@@ -4386,7 +4496,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:5" ht="14.25">
       <c r="B96" t="s">
         <v>274</v>
       </c>
@@ -4400,7 +4510,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:5" ht="14.25">
       <c r="B97" t="s">
         <v>276</v>
       </c>
@@ -4414,7 +4524,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:5" ht="14.25">
       <c r="B98" t="s">
         <v>278</v>
       </c>
@@ -4428,7 +4538,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:5" ht="14.25">
       <c r="B99" t="s">
         <v>280</v>
       </c>
@@ -4442,7 +4552,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:5" ht="14.25">
       <c r="B100" t="s">
         <v>282</v>
       </c>
@@ -4456,7 +4566,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:5" ht="14.25">
       <c r="B101" t="s">
         <v>284</v>
       </c>
@@ -4470,7 +4580,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:5" ht="14.25">
       <c r="B102" t="s">
         <v>286</v>
       </c>
@@ -4484,7 +4594,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:5" ht="14.25">
       <c r="B103" t="s">
         <v>288</v>
       </c>
@@ -4498,7 +4608,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:5" ht="14.25">
       <c r="B104" t="s">
         <v>290</v>
       </c>
@@ -4512,7 +4622,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:5" ht="14.25">
       <c r="B105" t="s">
         <v>292</v>
       </c>
@@ -4526,7 +4636,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:5" ht="14.25">
       <c r="B106" t="s">
         <v>294</v>
       </c>
@@ -4540,7 +4650,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:5" ht="14.25">
       <c r="B107" t="s">
         <v>296</v>
       </c>
@@ -4554,7 +4664,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:5" ht="14.25">
       <c r="B108" t="s">
         <v>298</v>
       </c>
@@ -4568,7 +4678,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:5" ht="14.25">
       <c r="B109" t="s">
         <v>300</v>
       </c>
@@ -4582,7 +4692,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:5" ht="14.25">
       <c r="B110" t="s">
         <v>302</v>
       </c>
@@ -4596,7 +4706,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:5" ht="14.25">
       <c r="B111" t="s">
         <v>304</v>
       </c>
@@ -4610,7 +4720,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:5" ht="14.25">
       <c r="B112" t="s">
         <v>306</v>
       </c>
@@ -4624,7 +4734,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:5" ht="14.25">
       <c r="B113" t="s">
         <v>308</v>
       </c>
@@ -4638,7 +4748,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:5" ht="14.25">
       <c r="B114" t="s">
         <v>310</v>
       </c>
@@ -4652,7 +4762,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:5" ht="14.25">
       <c r="B115" t="s">
         <v>312</v>
       </c>
@@ -4666,7 +4776,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:5" ht="14.25">
       <c r="B116" t="s">
         <v>314</v>
       </c>
@@ -4680,7 +4790,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:5" ht="14.25">
       <c r="B117" t="s">
         <v>316</v>
       </c>
@@ -4694,7 +4804,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:5" ht="14.25">
       <c r="B118" t="s">
         <v>318</v>
       </c>
@@ -4708,7 +4818,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:5" ht="14.25">
       <c r="B119" t="s">
         <v>320</v>
       </c>
@@ -4722,7 +4832,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:5" ht="14.25">
       <c r="B120" t="s">
         <v>322</v>
       </c>
@@ -4736,7 +4846,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:5" ht="14.25">
       <c r="B121" t="s">
         <v>324</v>
       </c>
@@ -4750,7 +4860,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:5" ht="14.25">
       <c r="B122" t="s">
         <v>326</v>
       </c>
@@ -4764,7 +4874,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:5" ht="14.25">
       <c r="B123" t="s">
         <v>328</v>
       </c>
@@ -4778,7 +4888,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:5" ht="14.25">
       <c r="B124" t="s">
         <v>330</v>
       </c>
@@ -4792,7 +4902,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:5" ht="14.25">
       <c r="B125" t="s">
         <v>332</v>
       </c>
@@ -4806,7 +4916,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:5" ht="14.25">
       <c r="B126" t="s">
         <v>334</v>
       </c>
@@ -4820,7 +4930,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:5" ht="14.25">
       <c r="B127" t="s">
         <v>336</v>
       </c>
@@ -4834,7 +4944,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:5" ht="14.25">
       <c r="B128" t="s">
         <v>338</v>
       </c>
@@ -4848,7 +4958,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:5" ht="14.25">
       <c r="B129" t="s">
         <v>340</v>
       </c>
@@ -4862,7 +4972,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:5" ht="14.25">
       <c r="B130" t="s">
         <v>342</v>
       </c>
@@ -4876,7 +4986,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:5" ht="14.25">
       <c r="B131" t="s">
         <v>344</v>
       </c>
@@ -4890,7 +5000,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:5" ht="14.25">
       <c r="B132" t="s">
         <v>346</v>
       </c>
@@ -4904,7 +5014,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:5" ht="14.25">
       <c r="B133" t="s">
         <v>348</v>
       </c>
@@ -4918,7 +5028,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:5" ht="14.25">
       <c r="B134" t="s">
         <v>350</v>
       </c>
@@ -4932,7 +5042,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:5" ht="14.25">
       <c r="B135" t="s">
         <v>352</v>
       </c>
@@ -4946,7 +5056,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:5" ht="14.25">
       <c r="B136" t="s">
         <v>354</v>
       </c>
@@ -4960,7 +5070,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:5" ht="14.25">
       <c r="B137" t="s">
         <v>356</v>
       </c>
@@ -4974,7 +5084,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:5" ht="14.25">
       <c r="B138" t="s">
         <v>358</v>
       </c>
@@ -4988,7 +5098,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:5" ht="14.25">
       <c r="B139" t="s">
         <v>360</v>
       </c>
@@ -5002,7 +5112,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:5" ht="14.25">
       <c r="B140" t="s">
         <v>362</v>
       </c>
@@ -5016,7 +5126,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:5" ht="14.25">
       <c r="B141" t="s">
         <v>364</v>
       </c>
@@ -5030,7 +5140,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:5" ht="14.25">
       <c r="B142" t="s">
         <v>366</v>
       </c>
@@ -5044,7 +5154,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:5" ht="14.25">
       <c r="B143" t="s">
         <v>368</v>
       </c>
@@ -5058,7 +5168,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:5" ht="14.25">
       <c r="B144" t="s">
         <v>370</v>
       </c>
@@ -5072,7 +5182,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:5" ht="14.25">
       <c r="B145" t="s">
         <v>372</v>
       </c>
@@ -5086,7 +5196,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:5" ht="14.25">
       <c r="B146" t="s">
         <v>374</v>
       </c>
@@ -5100,7 +5210,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:5" ht="14.25">
       <c r="B147" t="s">
         <v>376</v>
       </c>
@@ -5114,7 +5224,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:5" ht="14.25">
       <c r="B148" t="s">
         <v>378</v>
       </c>
@@ -5128,7 +5238,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:5" ht="14.25">
       <c r="B149" t="s">
         <v>380</v>
       </c>
@@ -5142,7 +5252,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:5" ht="14.25">
       <c r="B150" t="s">
         <v>382</v>
       </c>
@@ -5156,7 +5266,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:5" ht="14.25">
       <c r="B151" t="s">
         <v>384</v>
       </c>
@@ -5170,7 +5280,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:5" ht="14.25">
       <c r="B152" t="s">
         <v>386</v>
       </c>
@@ -5184,7 +5294,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:5" ht="14.25">
       <c r="B153" t="s">
         <v>388</v>
       </c>
@@ -5198,7 +5308,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:5" ht="14.25">
       <c r="B154" t="s">
         <v>390</v>
       </c>
@@ -5212,7 +5322,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:5" ht="14.25">
       <c r="B155" t="s">
         <v>392</v>
       </c>
@@ -5226,7 +5336,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:5" ht="14.25">
       <c r="B156" t="s">
         <v>394</v>
       </c>
@@ -5240,7 +5350,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:5" ht="14.25">
       <c r="B157" t="s">
         <v>396</v>
       </c>
@@ -5254,7 +5364,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:5" ht="14.25">
       <c r="B158" t="s">
         <v>398</v>
       </c>
@@ -5268,7 +5378,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:5" ht="14.25">
       <c r="B159" t="s">
         <v>400</v>
       </c>
@@ -5282,7 +5392,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:5" ht="14.25">
       <c r="B160" t="s">
         <v>402</v>
       </c>
@@ -5296,7 +5406,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:5" ht="14.25">
       <c r="B161" t="s">
         <v>404</v>
       </c>
@@ -5310,7 +5420,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:5" ht="14.25">
       <c r="B162" t="s">
         <v>406</v>
       </c>
@@ -5324,7 +5434,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:5" ht="14.25">
       <c r="B163" t="s">
         <v>408</v>
       </c>
@@ -5338,7 +5448,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:5" ht="14.25">
       <c r="B164" t="s">
         <v>410</v>
       </c>
@@ -5352,7 +5462,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:5" ht="14.25">
       <c r="B165" t="s">
         <v>412</v>
       </c>
@@ -5366,7 +5476,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:5" ht="14.25">
       <c r="B166" t="s">
         <v>414</v>
       </c>
@@ -5380,7 +5490,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:5" ht="14.25">
       <c r="B167" t="s">
         <v>416</v>
       </c>
@@ -5394,7 +5504,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:5" ht="14.25">
       <c r="B168" t="s">
         <v>418</v>
       </c>
@@ -5408,7 +5518,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:5" ht="14.25">
       <c r="B169" t="s">
         <v>420</v>
       </c>
@@ -5422,7 +5532,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:5" ht="14.25">
       <c r="B170" t="s">
         <v>422</v>
       </c>
@@ -5436,7 +5546,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:5" ht="14.25">
       <c r="B171" t="s">
         <v>424</v>
       </c>
@@ -5450,7 +5560,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:5" ht="14.25">
       <c r="B172" t="s">
         <v>426</v>
       </c>
@@ -5464,7 +5574,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:5" ht="14.25">
       <c r="B173" t="s">
         <v>428</v>
       </c>
@@ -5478,7 +5588,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:5" ht="14.25">
       <c r="B174" t="s">
         <v>430</v>
       </c>
@@ -5492,7 +5602,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:5" ht="14.25">
       <c r="B175" t="s">
         <v>432</v>
       </c>
@@ -5506,7 +5616,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:5" ht="14.25">
       <c r="B176" t="s">
         <v>434</v>
       </c>
@@ -5520,7 +5630,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:5" ht="14.25">
       <c r="B177" t="s">
         <v>436</v>
       </c>
@@ -5534,7 +5644,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:5" ht="14.25">
       <c r="B178" t="s">
         <v>438</v>
       </c>
@@ -5548,7 +5658,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:5" ht="14.25">
       <c r="B179" t="s">
         <v>440</v>
       </c>
@@ -5562,7 +5672,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:5" ht="14.25">
       <c r="B180" t="s">
         <v>442</v>
       </c>
@@ -5576,7 +5686,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:5" ht="14.25">
       <c r="B181" t="s">
         <v>444</v>
       </c>
@@ -5590,7 +5700,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:5" ht="14.25">
       <c r="B182" t="s">
         <v>446</v>
       </c>
@@ -5604,7 +5714,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:5" ht="14.25">
       <c r="B183" t="s">
         <v>448</v>
       </c>
@@ -5618,7 +5728,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:5" ht="14.25">
       <c r="B184" t="s">
         <v>450</v>
       </c>
@@ -5632,7 +5742,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:5" ht="14.25">
       <c r="B185" t="s">
         <v>452</v>
       </c>
@@ -5646,7 +5756,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:5" ht="14.25">
       <c r="B186" t="s">
         <v>454</v>
       </c>
@@ -5660,7 +5770,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:5" ht="14.25">
       <c r="B187" t="s">
         <v>456</v>
       </c>
@@ -5674,7 +5784,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:5" ht="14.25">
       <c r="B188" t="s">
         <v>458</v>
       </c>
@@ -5688,7 +5798,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:5" ht="14.25">
       <c r="B189" t="s">
         <v>460</v>
       </c>
@@ -5702,7 +5812,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:5" ht="14.25">
       <c r="B190" t="s">
         <v>462</v>
       </c>
@@ -5716,7 +5826,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:5" ht="14.25">
       <c r="B191" t="s">
         <v>464</v>
       </c>
@@ -5730,7 +5840,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:5" ht="14.25">
       <c r="B192" t="s">
         <v>466</v>
       </c>
@@ -5744,7 +5854,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:5" ht="14.25">
       <c r="B193" t="s">
         <v>468</v>
       </c>
@@ -5758,7 +5868,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:5" ht="14.25">
       <c r="B194" t="s">
         <v>470</v>
       </c>
@@ -5772,7 +5882,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:5" ht="14.25">
       <c r="B195" t="s">
         <v>472</v>
       </c>
@@ -5786,7 +5896,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:5" ht="14.25">
       <c r="B196" t="s">
         <v>474</v>
       </c>
@@ -5800,7 +5910,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:5" ht="14.25">
       <c r="B197" t="s">
         <v>476</v>
       </c>
@@ -5814,7 +5924,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:5" ht="14.25">
       <c r="B198" t="s">
         <v>478</v>
       </c>
@@ -5828,7 +5938,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:5" ht="14.25">
       <c r="B199" t="s">
         <v>480</v>
       </c>
@@ -5842,7 +5952,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:5" ht="14.25">
       <c r="B200" t="s">
         <v>482</v>
       </c>
@@ -5862,23 +5972,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71754C8A-E599-4286-919F-11B5789CC171}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71754C8A-E599-4286-919F-11B5789CC171}">
   <dimension ref="A1:K48"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="86" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.4285714285714" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" ht="17.25" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:10" ht="15" thickTop="1" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -5910,7 +6020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:9" ht="14.25">
       <c r="B3" t="s">
         <v>29</v>
       </c>
@@ -5927,7 +6037,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="14.25">
       <c r="B4" t="s">
         <v>22</v>
       </c>
@@ -5935,7 +6045,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" ht="14.25">
       <c r="B5" t="s">
         <v>23</v>
       </c>
@@ -5943,7 +6053,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:9" ht="14.25">
       <c r="B6" t="s">
         <v>30</v>
       </c>
@@ -5957,7 +6067,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" ht="14.25">
       <c r="B7" t="s">
         <v>31</v>
       </c>
@@ -5965,7 +6075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" ht="14.25">
       <c r="B8" t="s">
         <v>33</v>
       </c>
@@ -5973,7 +6083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="14.25">
       <c r="B9" t="s">
         <v>32</v>
       </c>
@@ -5981,7 +6091,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="14.25">
       <c r="B10" t="s">
         <v>28</v>
       </c>
@@ -5989,7 +6099,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="4:6" ht="14.25">
       <c r="D11" t="s">
         <v>40</v>
       </c>
@@ -5997,7 +6107,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:7" ht="14.25">
       <c r="B12" s="3"/>
       <c r="D12" t="s">
         <v>91</v>
@@ -6009,7 +6119,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="4:7" ht="14.25">
       <c r="D13" t="s">
         <v>92</v>
       </c>
@@ -6020,7 +6130,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="4:6" ht="14.25">
       <c r="D14" t="s">
         <v>41</v>
       </c>
@@ -6028,7 +6138,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" ht="14.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -6042,7 +6152,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" ht="14.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -6056,7 +6166,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:9" ht="14.25">
       <c r="B17" s="3" t="s">
         <v>79</v>
       </c>
@@ -6073,7 +6183,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" ht="14.25">
       <c r="B18" t="s">
         <v>77</v>
       </c>
@@ -6084,7 +6194,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="14.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -6095,7 +6205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" ht="14.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -6112,7 +6222,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" ht="14.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -6123,7 +6233,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="14.25">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -6134,7 +6244,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="14.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -6142,7 +6252,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" ht="14.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -6153,7 +6263,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" ht="14.25">
       <c r="A25" t="s">
         <v>69</v>
       </c>
@@ -6164,7 +6274,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:11" ht="14.25">
       <c r="B26" t="str">
         <f>"g[_]*"&amp;K26</f>
         <v>g[_]*220</v>
@@ -6177,20 +6287,20 @@
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:11" ht="14.25">
       <c r="B27" t="str">
-        <f t="shared" ref="B27:B46" si="0">"g[_]*"&amp;K27</f>
+        <f t="shared" si="0" ref="B27:B46">"g[_]*"&amp;K27</f>
         <v>g[_]*400</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" ref="F27:F46" si="1">"Grid-"&amp;K27&amp;"V"</f>
+        <f t="shared" si="1" ref="F27:F46">"Grid-"&amp;K27&amp;"V"</f>
         <v>Grid-400V</v>
       </c>
       <c r="K27">
         <v>400</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:11" ht="14.25">
       <c r="B28" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*380</v>
@@ -6203,7 +6313,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:11" ht="14.25">
       <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*225</v>
@@ -6216,7 +6326,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:11" ht="14.25">
       <c r="B30" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*330</v>
@@ -6229,7 +6339,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:11" ht="14.25">
       <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*275</v>
@@ -6242,7 +6352,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:11" ht="14.25">
       <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*420</v>
@@ -6255,7 +6365,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:11" ht="14.25">
       <c r="B33" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*300</v>
@@ -6268,7 +6378,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:11" ht="14.25">
       <c r="B34" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*500</v>
@@ -6281,7 +6391,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:11" ht="14.25">
       <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*750</v>
@@ -6294,7 +6404,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:11" ht="14.25">
       <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*450</v>
@@ -6307,7 +6417,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:11" ht="14.25">
       <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*515</v>
@@ -6320,7 +6430,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:11" ht="14.25">
       <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*525</v>
@@ -6333,7 +6443,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:11" ht="14.25">
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*320</v>
@@ -6346,7 +6456,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:11" ht="14.25">
       <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*150</v>
@@ -6359,7 +6469,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:11" ht="14.25">
       <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*270</v>
@@ -6372,7 +6482,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:11" ht="14.25">
       <c r="B42" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*350</v>
@@ -6385,7 +6495,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:11" ht="14.25">
       <c r="B43" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*250</v>
@@ -6398,7 +6508,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:11" ht="14.25">
       <c r="B44" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*200</v>
@@ -6411,7 +6521,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:11" ht="14.25">
       <c r="B45" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*236</v>
@@ -6424,7 +6534,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:11" ht="14.25">
       <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>g[_]*600</v>
@@ -6437,7 +6547,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:6" ht="14.25">
       <c r="B47" t="s">
         <v>97</v>
       </c>
@@ -6445,7 +6555,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:6" ht="14.25">
       <c r="B48" t="s">
         <v>86</v>
       </c>
@@ -6459,29 +6569,29 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A236EA34-5180-48E7-B945-13E283806401}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A236EA34-5180-48E7-B945-13E283806401}">
   <dimension ref="A1:K75"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.4285714285714" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.57142857142857" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5714285714286" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.86328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.14285714285714" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="14.25">
       <c r="A1" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="14.25">
       <c r="A2" t="s">
         <v>485</v>
       </c>
@@ -6516,9 +6626,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="5:11" ht="14.25">
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E9" si="0">"E_"&amp;SUBSTITUTE(F3," ","")</f>
+        <f t="shared" si="0" ref="E3:E9">"E_"&amp;SUBSTITUTE(F3," ","")</f>
         <v>E_Bio</v>
       </c>
       <c r="F3" t="s">
@@ -6531,7 +6641,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="5:11" ht="14.25">
       <c r="E4" t="str">
         <f t="shared" si="0"/>
         <v>E_Biogas</v>
@@ -6546,7 +6656,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="5:11" ht="14.25">
       <c r="E5" t="str">
         <f t="shared" si="0"/>
         <v>E_Coal</v>
@@ -6561,7 +6671,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="5:11" ht="14.25">
       <c r="E6" t="str">
         <f t="shared" si="0"/>
         <v>E_Geothermal</v>
@@ -6576,7 +6686,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="5:11" ht="14.25">
       <c r="E7" t="str">
         <f t="shared" si="0"/>
         <v>E_Hydro</v>
@@ -6591,7 +6701,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="5:11" ht="14.25">
       <c r="E8" t="str">
         <f t="shared" si="0"/>
         <v>E_NaturalGas</v>
@@ -6606,7 +6716,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="5:11" ht="14.25">
       <c r="E9" t="str">
         <f t="shared" si="0"/>
         <v>E_Solar</v>
@@ -6621,7 +6731,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="5:8" ht="14.25">
       <c r="E10" t="s">
         <v>506</v>
       </c>
@@ -6635,7 +6745,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="5:8" ht="14.25">
       <c r="E11" t="s">
         <v>509</v>
       </c>
@@ -6649,7 +6759,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="5:11" ht="14.25">
       <c r="E12" t="str">
         <f>"E_"&amp;SUBSTITUTE(F12," ","")</f>
         <v>E_Waste</v>
@@ -6664,7 +6774,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="5:11" ht="14.25">
       <c r="E13" t="str">
         <f>"E_"&amp;SUBSTITUTE(F13," ","")</f>
         <v>E_Wind</v>
@@ -6679,7 +6789,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="5:10" ht="14.25">
       <c r="E14" t="str">
         <f>"eu_"&amp;F14</f>
         <v>eu_Aviation</v>
@@ -6694,7 +6804,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="5:10" ht="14.25">
       <c r="E15" t="str">
         <f>"eu_"&amp;F15</f>
         <v>eu_Bus</v>
@@ -6709,7 +6819,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="5:10" ht="14.25">
       <c r="E16" t="str">
         <f>"eu_"&amp;F16</f>
         <v>eu_Cars</v>
@@ -6724,7 +6834,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="17" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="5:10" ht="14.25">
       <c r="E17" t="s">
         <v>522</v>
       </c>
@@ -6738,7 +6848,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="18" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="5:10" ht="14.25">
       <c r="E18" t="s">
         <v>525</v>
       </c>
@@ -6752,7 +6862,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="19" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="5:10" ht="14.25">
       <c r="E19" t="s">
         <v>528</v>
       </c>
@@ -6766,7 +6876,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="20" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="5:10" ht="14.25">
       <c r="E20" t="s">
         <v>531</v>
       </c>
@@ -6780,7 +6890,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="21" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="5:10" ht="14.25">
       <c r="E21" t="s">
         <v>534</v>
       </c>
@@ -6794,7 +6904,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="22" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="5:10" ht="14.25">
       <c r="E22" t="s">
         <v>537</v>
       </c>
@@ -6808,7 +6918,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="23" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="5:10" ht="14.25">
       <c r="E23" t="s">
         <v>540</v>
       </c>
@@ -6822,7 +6932,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="24" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="5:10" ht="14.25">
       <c r="E24" t="str">
         <f>"eu_"&amp;F24</f>
         <v>eu_Motorcycle</v>
@@ -6837,7 +6947,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="25" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="5:10" ht="14.25">
       <c r="E25" t="s">
         <v>545</v>
       </c>
@@ -6851,7 +6961,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="26" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="5:10" ht="14.25">
       <c r="E26" t="s">
         <v>548</v>
       </c>
@@ -6865,7 +6975,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="27" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="5:10" ht="14.25">
       <c r="E27" t="str">
         <f>"eu_"&amp;F27</f>
         <v>eu_Rail</v>
@@ -6880,7 +6990,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="28" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="5:10" ht="14.25">
       <c r="E28" t="s">
         <v>553</v>
       </c>
@@ -6894,7 +7004,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="29" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="5:10" ht="14.25">
       <c r="E29" t="str">
         <f>"eu_"&amp;F29</f>
         <v>eu_Ships</v>
@@ -6909,7 +7019,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="30" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="5:10" ht="14.25">
       <c r="E30" t="s">
         <v>558</v>
       </c>
@@ -6923,7 +7033,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="31" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="5:10" ht="14.25">
       <c r="E31" t="s">
         <v>561</v>
       </c>
@@ -6937,7 +7047,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="32" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="5:10" ht="14.25">
       <c r="E32" t="str">
         <f>"eu_"&amp;F32</f>
         <v>eu_Trucks</v>
@@ -6952,7 +7062,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="33" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="5:10" ht="14.25">
       <c r="E33" t="s">
         <v>566</v>
       </c>
@@ -6966,7 +7076,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="34" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="5:10" ht="14.25">
       <c r="E34" t="s">
         <v>569</v>
       </c>
@@ -6980,7 +7090,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="35" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="5:9" ht="14.25">
       <c r="E35" t="s">
         <v>572</v>
       </c>
@@ -6997,7 +7107,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="36" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="5:10" ht="14.25">
       <c r="E36" t="s">
         <v>576</v>
       </c>
@@ -7011,7 +7121,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="37" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="5:8" ht="14.25">
       <c r="E37" t="s">
         <v>579</v>
       </c>
@@ -7025,7 +7135,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="38" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="5:11" ht="14.25">
       <c r="E38" t="s">
         <v>582</v>
       </c>
@@ -7039,7 +7149,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="39" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="5:7" ht="14.25">
       <c r="E39" t="s">
         <v>585</v>
       </c>
@@ -7050,7 +7160,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="40" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="5:8" ht="14.25">
       <c r="E40" t="s">
         <v>588</v>
       </c>
@@ -7064,7 +7174,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="41" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="5:8" ht="14.25">
       <c r="E41" t="s">
         <v>591</v>
       </c>
@@ -7078,7 +7188,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="42" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="5:8" ht="14.25">
       <c r="E42" t="s">
         <v>594</v>
       </c>
@@ -7092,7 +7202,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="43" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="5:8" ht="14.25">
       <c r="E43" t="s">
         <v>597</v>
       </c>
@@ -7106,7 +7216,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="44" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="5:10" ht="14.25">
       <c r="E44" t="s">
         <v>600</v>
       </c>
@@ -7120,7 +7230,19 @@
         <v>602</v>
       </c>
     </row>
-    <row r="45" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" ht="14.25">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" t="s">
+        <v>45</v>
+      </c>
       <c r="E45" t="s">
         <v>603</v>
       </c>
@@ -7130,8 +7252,23 @@
       <c r="G45" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="46" spans="5:11" x14ac:dyDescent="0.45">
+      <c r="H45" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="14.25">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" t="s">
+        <v>45</v>
+      </c>
       <c r="E46" t="s">
         <v>605</v>
       </c>
@@ -7139,13 +7276,13 @@
         <v>606</v>
       </c>
       <c r="G46" t="s">
-        <v>49</v>
+        <v>758</v>
       </c>
       <c r="J46" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="47" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="47" spans="5:10" ht="14.25">
       <c r="E47" t="str">
         <f>"ss_"&amp;SUBSTITUTE(F47," ","")</f>
         <v>ss_Attached</v>
@@ -7160,7 +7297,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="48" spans="5:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="5:8" ht="14.25">
       <c r="E48" t="s">
         <v>610</v>
       </c>
@@ -7174,7 +7311,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="49" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="5:8" ht="14.25">
       <c r="E49" t="s">
         <v>613</v>
       </c>
@@ -7188,7 +7325,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="50" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="5:8" ht="14.25">
       <c r="E50" t="s">
         <v>616</v>
       </c>
@@ -7202,7 +7339,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="51" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="5:10" ht="14.25">
       <c r="E51" t="str">
         <f>"ss_"&amp;SUBSTITUTE(F51," ","")</f>
         <v>ss_DairyCattleFarming</v>
@@ -7217,7 +7354,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="52" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="5:10" ht="14.25">
       <c r="E52" t="str">
         <f>"ss_"&amp;SUBSTITUTE(F52," ","")</f>
         <v>ss_Detached</v>
@@ -7232,7 +7369,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="53" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="5:10" ht="14.25">
       <c r="E53" t="str">
         <f>"ss_"&amp;SUBSTITUTE(F53," ","")</f>
         <v>ss_Education</v>
@@ -7247,7 +7384,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="54" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="5:10" ht="14.25">
       <c r="E54" t="str">
         <f>"ss_"&amp;SUBSTITUTE(F54," ","")</f>
         <v>ss_Fishing</v>
@@ -7262,7 +7399,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="55" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="5:8" ht="14.25">
       <c r="E55" t="s">
         <v>627</v>
       </c>
@@ -7276,9 +7413,9 @@
         <v>629</v>
       </c>
     </row>
-    <row r="56" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="5:10" ht="14.25">
       <c r="E56" t="str">
-        <f t="shared" ref="E56:E69" si="1">"ss_"&amp;SUBSTITUTE(F56," ","")</f>
+        <f t="shared" si="1" ref="E56:E69">"ss_"&amp;SUBSTITUTE(F56," ","")</f>
         <v>ss_Forestry</v>
       </c>
       <c r="F56" t="s">
@@ -7291,7 +7428,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="57" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="5:10" ht="14.25">
       <c r="E57" t="str">
         <f t="shared" si="1"/>
         <v>ss_Healthcare</v>
@@ -7306,7 +7443,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="58" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="5:10" ht="14.25">
       <c r="E58" t="str">
         <f t="shared" si="1"/>
         <v>ss_Horticulture</v>
@@ -7321,7 +7458,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="59" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="5:10" ht="14.25">
       <c r="E59" t="str">
         <f t="shared" si="1"/>
         <v>ss_Indoorcropping</v>
@@ -7336,7 +7473,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="60" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="5:10" ht="14.25">
       <c r="E60" t="str">
         <f t="shared" si="1"/>
         <v>ss_Livestock</v>
@@ -7351,7 +7488,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="61" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="5:8" ht="14.25">
       <c r="E61" t="str">
         <f t="shared" si="1"/>
         <v>ss_Meat</v>
@@ -7366,7 +7503,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="62" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="5:8" ht="14.25">
       <c r="E62" t="str">
         <f t="shared" si="1"/>
         <v>ss_Metals</v>
@@ -7381,7 +7518,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="63" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="5:8" ht="14.25">
       <c r="E63" t="str">
         <f t="shared" si="1"/>
         <v>ss_Methanol</v>
@@ -7396,7 +7533,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="64" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="5:8" ht="14.25">
       <c r="E64" t="str">
         <f t="shared" si="1"/>
         <v>ss_Minerals</v>
@@ -7411,7 +7548,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="65" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="5:8" ht="14.25">
       <c r="E65" t="str">
         <f t="shared" si="1"/>
         <v>ss_Mining</v>
@@ -7426,7 +7563,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="66" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="5:10" ht="14.25">
       <c r="E66" t="str">
         <f t="shared" si="1"/>
         <v>ss_Office</v>
@@ -7441,7 +7578,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="67" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="5:8" ht="14.25">
       <c r="E67" t="str">
         <f t="shared" si="1"/>
         <v>ss_OtherInd</v>
@@ -7456,7 +7593,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="68" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="5:10" ht="14.25">
       <c r="E68" t="str">
         <f t="shared" si="1"/>
         <v>ss_OtherAgri</v>
@@ -7471,7 +7608,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="69" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="5:10" ht="14.25">
       <c r="E69" t="str">
         <f t="shared" si="1"/>
         <v>ss_OtherCom</v>
@@ -7486,7 +7623,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="70" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="5:8" ht="14.25">
       <c r="E70" t="s">
         <v>658</v>
       </c>
@@ -7500,7 +7637,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="71" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="5:8" ht="14.25">
       <c r="E71" t="str">
         <f>"ss_"&amp;SUBSTITUTE(F71," ","")</f>
         <v>ss_Refining</v>
@@ -7515,7 +7652,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="72" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="5:8" ht="14.25">
       <c r="E72" t="s">
         <v>663</v>
       </c>
@@ -7529,7 +7666,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="73" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="5:8" ht="14.25">
       <c r="E73" t="str">
         <f>"ss_"&amp;SUBSTITUTE(F73," ","")</f>
         <v>ss_Urea</v>
@@ -7544,7 +7681,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="74" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="5:8" ht="14.25">
       <c r="E74" t="str">
         <f>"ss_"&amp;SUBSTITUTE(F74," ","")</f>
         <v>ss_WoodProdMfg</v>
@@ -7559,7 +7696,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="75" spans="5:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="5:10" ht="14.25">
       <c r="E75" t="str">
         <f>"ss_"&amp;SUBSTITUTE(F75," ","")</f>
         <v>ss_WSR</v>
@@ -7580,19 +7717,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F3D05A-3957-4820-93DE-DB11637970DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F3D05A-3957-4820-93DE-DB11637970DC}">
   <dimension ref="A1:O49"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="35.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.4285714285714" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="14.25">
       <c r="A1" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="14.25">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -7621,7 +7758,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" ht="14.25">
       <c r="A3" t="str">
         <f>"nrg_"&amp;N3</f>
         <v>nrg_COA</v>
@@ -7644,20 +7781,20 @@
         <v>496</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" ht="14.25">
       <c r="A4" t="str">
-        <f t="shared" ref="A4:A39" si="0">"nrg_"&amp;N4</f>
+        <f t="shared" si="0" ref="A4:A39">"nrg_"&amp;N4</f>
         <v>nrg_DSL</v>
       </c>
       <c r="B4" t="str">
-        <f t="shared" ref="B4:B39" si="1">O4</f>
+        <f t="shared" si="1" ref="B4:B39">O4</f>
         <v>Diesel</v>
       </c>
       <c r="C4" t="s">
         <v>680</v>
       </c>
       <c r="D4" t="str">
-        <f t="shared" ref="D4:D39" si="2">"*"&amp;N4</f>
+        <f t="shared" si="2" ref="D4:D39">"*"&amp;N4</f>
         <v>*DSL</v>
       </c>
       <c r="N4" s="5" t="s">
@@ -7667,21 +7804,30 @@
         <v>683</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
-        <f t="shared" si="0"/>
-        <v>nrg_ELC</v>
-      </c>
-      <c r="B5" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">Electricity </v>
+    <row r="5" spans="1:15" ht="14.25">
+      <c r="A5" t="s">
+        <v>759</v>
+      </c>
+      <c r="B5" t="s">
+        <v>760</v>
       </c>
       <c r="C5" t="s">
         <v>680</v>
       </c>
-      <c r="D5" t="str">
-        <f t="shared" si="2"/>
-        <v>*ELC</v>
+      <c r="D5" t="s">
+        <v>761</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>55</v>
@@ -7690,7 +7836,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" ht="14.25">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>nrg_FOL</v>
@@ -7713,7 +7859,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" ht="14.25">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>nrg_GEO</v>
@@ -7736,7 +7882,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" ht="14.25">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>nrg_H2R</v>
@@ -7759,7 +7905,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" ht="14.25">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>nrg_LPG</v>
@@ -7782,7 +7928,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" ht="14.25">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>nrg_NGA</v>
@@ -7805,7 +7951,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" ht="14.25">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>nrg_PET</v>
@@ -7828,7 +7974,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" ht="14.25">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>nrg_PLT</v>
@@ -7851,7 +7997,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" ht="14.25">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>nrg_WOD</v>
@@ -7874,7 +8020,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" ht="14.25">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>nrg_WST</v>
@@ -7897,7 +8043,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" ht="14.25">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>nrg_MNR</v>
@@ -7920,7 +8066,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" ht="14.25">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>nrg_BIG</v>
@@ -7943,7 +8089,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" ht="14.25">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>nrg_BIL</v>
@@ -7966,7 +8112,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" ht="14.25">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>nrg_COL</v>
@@ -7989,7 +8135,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" ht="14.25">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>nrg_seq</v>
@@ -8012,7 +8158,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" ht="14.25">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>nrg_CO2</v>
@@ -8035,7 +8181,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" ht="14.25">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>nrg_DID</v>
@@ -8058,7 +8204,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" ht="14.25">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>nrg_DIJ</v>
@@ -8081,7 +8227,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:15" ht="14.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>nrg_LCD</v>
@@ -8104,7 +8250,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" ht="14.25">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>nrg_CDD</v>
@@ -8127,7 +8273,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" ht="14.25">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>nrg_-HV</v>
@@ -8150,7 +8296,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" ht="14.25">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>nrg_HYD</v>
@@ -8173,7 +8319,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" ht="14.25">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>nrg_-MV</v>
@@ -8196,7 +8342,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" ht="14.25">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>nrg_OIL</v>
@@ -8219,7 +8365,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" ht="14.25">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>nrg_SOL</v>
@@ -8242,7 +8388,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:15" ht="14.25">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>nrg_TID</v>
@@ -8265,7 +8411,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:15" ht="14.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>nrg_URN</v>
@@ -8288,7 +8434,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:15" ht="14.25">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>nrg_WIN</v>
@@ -8311,7 +8457,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:15" ht="14.25">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>nrg_H2C</v>
@@ -8334,7 +8480,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:15" ht="14.25">
       <c r="A34" t="str">
         <f t="shared" si="0"/>
         <v>nrg_H2D</v>
@@ -8357,7 +8503,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:15" ht="14.25">
       <c r="A35" t="str">
         <f t="shared" si="0"/>
         <v>nrg_JET</v>
@@ -8380,7 +8526,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:15" ht="14.25">
       <c r="A36" t="str">
         <f t="shared" si="0"/>
         <v>nrg_LNG</v>
@@ -8403,7 +8549,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:15" ht="14.25">
       <c r="A37" t="str">
         <f t="shared" si="0"/>
         <v>nrg_ILD</v>
@@ -8426,7 +8572,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:15" ht="14.25">
       <c r="A38" t="str">
         <f t="shared" si="0"/>
         <v>nrg_ILI</v>
@@ -8449,7 +8595,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:15" ht="14.25">
       <c r="A39" t="str">
         <f t="shared" si="0"/>
         <v>nrg_OTH</v>
@@ -8472,7 +8618,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:15" ht="14.25">
       <c r="A40" t="str">
         <f>"dem_"&amp;N40</f>
         <v>dem_agriculture</v>
@@ -8495,7 +8641,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:15" ht="14.25">
       <c r="A41" t="str">
         <f>"dem_"&amp;N41</f>
         <v>dem_commercial</v>
@@ -8518,7 +8664,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:15" ht="14.25">
       <c r="A42" t="str">
         <f>"dem_"&amp;N42</f>
         <v>dem_industry</v>
@@ -8541,7 +8687,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:15" ht="14.25">
       <c r="A43" t="str">
         <f>"dem_"&amp;N43</f>
         <v>dem_residential</v>
@@ -8564,7 +8710,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:15" ht="14.25">
       <c r="A44" t="str">
         <f>"dem_"&amp;N44</f>
         <v>dem_transport</v>
@@ -8587,7 +8733,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" ht="14.25">
       <c r="A45" t="s">
         <v>748</v>
       </c>
@@ -8598,7 +8744,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" ht="14.25">
       <c r="A46" t="s">
         <v>750</v>
       </c>
@@ -8609,7 +8755,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" ht="14.25">
       <c r="A47" t="s">
         <v>752</v>
       </c>
@@ -8620,7 +8766,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" ht="14.25">
       <c r="A48" t="s">
         <v>753</v>
       </c>
@@ -8631,7 +8777,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" ht="14.25">
       <c r="A49" t="s">
         <v>755</v>
       </c>
@@ -8640,6 +8786,18 @@
       </c>
       <c r="D49" t="s">
         <v>756</v>
+      </c>
+      <c r="F49" t="s">
+        <v>44</v>
+      </c>
+      <c r="G49" t="s">
+        <v>44</v>
+      </c>
+      <c r="H49" t="s">
+        <v>45</v>
+      </c>
+      <c r="I49" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
